--- a/data/emails_classificacao.xlsx
+++ b/data/emails_classificacao.xlsx
@@ -396,8 +396,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:N23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,19 +445,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>21173</v>
+        <v>22545</v>
       </c>
       <c r="B2" t="str">
-        <v>Wed, 16 Oct 2024 17:16:51 +0100</v>
+        <v>Fri, 14 Mar 2025 02:51:41 +0100</v>
       </c>
       <c r="C2" t="str">
-        <v>"GLOBALBRICO Geral" &lt;geral@globalbrico.pt&gt;</v>
+        <v>"Unipessoal Lda" &lt;hamish@golfnuts.co.uk&gt;</v>
       </c>
       <c r="D2" t="str">
-        <v>FW: Pedido de Cotação-24100004 18/10/2024</v>
+        <v>Regularização  - 02:51:40.</v>
       </c>
       <c r="E2" t="str">
-        <v>Com os melhores cumprimentos, De: JORGE MIGUEL REIS Enviada: 16 de outubro de 2024 11:34 Para: undisclosed-recipients: Assunto: Pedido de Cotação-24100004 18/10/2024 Bom dia, Em anexo o n/ped. de cotação 24100004, agradeço resposta até 18/10/2024. * Mencionar o n/nº de consulta * Indicar o prazo de entrega Jorge Miguel Reis Armazém / Aprovisionamentos miguelreis@sopac.pt + 351 265 030 498 Rua do Rio Mondego Parque Ind. Sapec-Bay 2910-543 Setúbal fertiberia.com/adp-fertilizantes/ De acordo com a legislação em vigor em matéria de Proteção de Dados Pessoais, informamos que os dados pessoais contidos nesta comunicação estão incorporados num ficheiro cujo responsável é a SOPAC, S.A., cuja finalidade é o correto desenvolvimento das relações comerciais, profissionais e/ou de negócio; apenas serão cedidos a empresas do grupo com a mesma finalidade, não serão cedidos ou transmitidos a terceiros, salvo obrigação legal, e serão conservados enquanto não for solicitada a sua eliminação. Informamos, ainda, que a SOPAC, S.A. adotou as medidas de segurança adequadas nas suas instalações, sistemas, tratamentos e arquivos, garantindo a confidencialidade dos seus dados. Tem o direito de obter a confirmação sobre se a SOPAC, S.A. se encontra a proceder ao tratamento dos seus dados pessoais, pelo que tem o direito de aceder aos mesmos, retificando os dados incorretos ou solicitando a sua eliminação quando já não sejam necessários, podendo fazê-lo através do endereço de e-mail protecaodedados@adp-fertilizantes.pt. O conteúdo deste e-mail e respetivos anexos são estritamente confidenciais. Caso não seja o destinatário e tenha recebido esta mensagem por engano, agradeceríamos que informasse imediatamente o remetente, sem divulgar, armazenar ou copiar seu conteúdo. Information is marked as Restricted and belongs to Fertiberia Group</v>
+        <v>Senhora, Senhor, Através deste e-mail, gostaríamos de lhe recordar que ainda tem um saldo por regularizar connosco. Em anexo, encontrará uma cópia da fatura 2024-1373 de 18/12/2024 . Pedimos-lhe que, por favor, proceda à regularização desta situação com a maior brevidade possível. Se já efetuou o pagamento ou deu ordem para o mesmo, agradecemos e pode considerar este aviso sem efeito. Caso tenha alguma dúvida relativamente a esta fatura, não hesite em contactar-nos. Com os melhores cumprimentos,</v>
       </c>
       <c r="F2" t="str">
         <v>SPAM</v>
@@ -484,27 +484,27 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/21173.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/22545.json</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>21288</v>
+        <v>22561</v>
       </c>
       <c r="B3" t="str">
-        <v>Tue, 29 Oct 2024 16:31:09 +0100</v>
+        <v>Sat, 15 Mar 2025 10:39:28 +0100</v>
       </c>
       <c r="C3" t="str">
-        <v>"Antonio Tavares" &lt;antonio.tavares@progresso.pt&gt;</v>
+        <v>"Unipessoal Lda" &lt;mjc@mottramjiveclub.org.uk&gt;</v>
       </c>
       <c r="D3" t="str">
-        <v>Pedido de Cotação -RFQ/2024/10/29</v>
+        <v>Regularização  - 10:39:27.</v>
       </c>
       <c r="E3" t="str">
-        <v>Boa tarde, Agradecemos o vosso melhor preço e prazo de entrega para o pedido de cotação que segue anexo. Com os Melhores Cumprimentos, [1] Links: ------ [1] http://www.progresso.pt/</v>
+        <v>Senhora, Senhor, Através deste e-mail, gostaríamos de lhe recordar que ainda tem um saldo por regularizar connosco. Em anexo, encontrará uma cópia da fatura 2024-1373 de 18/12/2024 . Pedimos-lhe que, por favor, proceda à regularização desta situação com a maior brevidade possível. Se já efetuou o pagamento ou deu ordem para o mesmo, agradecemos e pode considerar este aviso sem efeito. Caso tenha alguma dúvida relativamente a esta fatura, não hesite em contactar-nos. Com os melhores cumprimentos,</v>
       </c>
       <c r="F3" t="str">
-        <v>Pedido de Informação</v>
+        <v>SPAM</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -528,27 +528,27 @@
         <v/>
       </c>
       <c r="N3" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/21288.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/22561.json</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>22545</v>
+        <v>25980</v>
       </c>
       <c r="B4" t="str">
-        <v>Fri, 14 Mar 2025 02:51:41 +0100</v>
+        <v>Mon, 30 Mar 2026 11:42:00 +0000</v>
       </c>
       <c r="C4" t="str">
-        <v>"Unipessoal Lda" &lt;hamish@golfnuts.co.uk&gt;</v>
+        <v>"Luisr Silva" &lt;luisr.silva@braga.pt&gt;</v>
       </c>
       <c r="D4" t="str">
-        <v>Regularização  - 02:51:40.</v>
+        <v>***SPAM***  Genehmigte Projektlieferung für aktuelles Verkaufsangebot: Folgeauftrag zur vorherigen Anfrage (SQ-202604)</v>
       </c>
       <c r="E4" t="str">
-        <v>Senhora, Senhor, Através deste e-mail, gostaríamos de lhe recordar que ainda tem um saldo por regularizar connosco. Em anexo, encontrará uma cópia da fatura 2024-1373 de 18/12/2024 . Pedimos-lhe que, por favor, proceda à regularização desta situação com a maior brevidade possível. Se já efetuou o pagamento ou deu ordem para o mesmo, agradecemos e pode considerar este aviso sem efeito. Caso tenha alguma dúvida relativamente a esta fatura, não hesite em contactar-nos. Com os melhores cumprimentos,</v>
+        <v>Saudações de Braga, Estamos entrando em contato após nossa conversa telefônica com seu colega sobre o novo pedido. Compilamos uma lista de requisitos que são urgentemente necessários. Por favor, verifique o arquivo anexo para todas as especificações e forneça mais detalhes com os termos de preço para prosseguirmos com o pedido. Atenciosamente, Luís Silva Técnico Superior luisr.silva@braga.pt T: 253 61 60 60 | Ext: 1108 www.braga.pt [1] Este e-mail é amigo do ambiente, pondere antes de o imprimir! CONFIDENCIALIDADE E PRIVACIDADE: Esta mensagem destina-se exclusivamente a quem nela conste como destinatário, contém informação confidencial, encontra-se protegida por segredo profissional e pode conter dados pessoais, sendo a sua divulgação proibida por lei. Caso não seja o destinatário desta mensagem agradecemos que a elimine imediatamente do seu sistema e informe o remetente, via e-mail ou telefone. Para informações sobre as práticas de privacidade do Município de Braga, consulte a Política de Privacidade [2]. Links: ------ [1] http://www.braga.pt/ [2] https://www.cm-braga.pt/pt/0503/politica-de-privacidade</v>
       </c>
       <c r="F4" t="str">
-        <v>SPAM</v>
+        <v>Pedido de Informação</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -572,27 +572,27 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/22545.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/25980.json</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>22561</v>
+        <v>26004</v>
       </c>
       <c r="B5" t="str">
-        <v>Sat, 15 Mar 2025 10:39:28 +0100</v>
+        <v>Wed, 01 Apr 2026 10:04:22 +0000</v>
       </c>
       <c r="C5" t="str">
-        <v>"Unipessoal Lda" &lt;mjc@mottramjiveclub.org.uk&gt;</v>
+        <v>"Raul Figueiredo" &lt;raulfigueiredo@enercon.de&gt;</v>
       </c>
       <c r="D5" t="str">
-        <v>Regularização  - 10:39:27.</v>
+        <v>***SPAM***  Verkaufsangebot RFQ-2501524: 04_2026_LPO Lieferung von PROJEKTARTIKELN in großen Mengen</v>
       </c>
       <c r="E5" t="str">
-        <v>Senhora, Senhor, Através deste e-mail, gostaríamos de lhe recordar que ainda tem um saldo por regularizar connosco. Em anexo, encontrará uma cópia da fatura 2024-1373 de 18/12/2024 . Pedimos-lhe que, por favor, proceda à regularização desta situação com a maior brevidade possível. Se já efetuou o pagamento ou deu ordem para o mesmo, agradecemos e pode considerar este aviso sem efeito. Caso tenha alguma dúvida relativamente a esta fatura, não hesite em contactar-nos. Com os melhores cumprimentos,</v>
+        <v>Bom dia,, Bom dia, Esta é uma resposta à nossa mensagem anterior, enviada pelo nosso departamento de compras, referente à sua lista de preços e fornecimento. Estamos prontos para prosseguir com o pedido. Todos os detalhes estão no arquivo anexo. Extraia o arquivo para visualizar os detalhes. Por favor, prossiga com a preparação da ordem de compra e confirme se os preços são os mesmos. Aguardamos sua resposta o mais breve possível. Os melhores cumprimentos / Best regards / Mit freundlichen Grüßen Raul Figueiredo Service Operations - Regional Lead Southern Europe &amp; Latin America Mobile : +351 912 746 580 (Quick Dial 2158) mailto : raulfigueiredo@enercon.de</v>
       </c>
       <c r="F5" t="str">
-        <v>SPAM</v>
+        <v>Pedido de Encomenda</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -616,27 +616,27 @@
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/22561.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26004.json</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>22683</v>
+        <v>26007</v>
       </c>
       <c r="B6" t="str">
-        <v>Tue, 25 Mar 2025 16:28:13 +0100</v>
+        <v>Wed, 01 Apr 2026 11:52:27 +0000</v>
       </c>
       <c r="C6" t="str">
-        <v>"Jorge Miguel" &lt;miguelreis@sopac.pt&gt;</v>
+        <v>"Tania Raimundo" &lt;taniarai@dav.pt&gt;</v>
       </c>
       <c r="D6" t="str">
-        <v>Pedido de Cotação-250325</v>
+        <v>***SPAM***  Re: Solicitação de Cotação: Confirmação do pedido de consulta - 1- 616195SFMS-2026, Fornecimento de Novo Lote</v>
       </c>
       <c r="E6" t="str">
-        <v>Boa Tarde, Em anexo o n/ped. de cotação 250325, agradeço resposta até 31/03/2025. * Mencionar o n/nº de consulta * Indicar o prazo de entrega Jorge Miguel Reis Armazém / Aprovisionamentos miguelreis@sopac.pt + 351 265 030 498 Rua do Rio Mondego Parque Ind. Sapec-Bay 2910-543 Setúbal fertiberia.com/adp-fertilizantes/ [1] [2] [3] [4] De acordo com a legislação em vigor em matéria de Proteção de Dados Pessoais, informamos que os dados pessoais contidos nesta comunicação estão incorporados num ficheiro cujo responsável é a SOPAC, S.A., cuja finalidade é o correto desenvolvimento das relações comerciais, profissionais e/ou de negócio; apenas serão cedidos a empresas do grupo com a mesma finalidade, não serão cedidos ou transmitidos a terceiros, salvo obrigação legal, e serão conservados enquanto não for solicitada a sua eliminação. Informamos, ainda, que a SOPAC, S.A. adotou as medidas de segurança adequadas nas suas instalações, sistemas, tratamentos e arquivos, garantindo a confidencialidade dos seus dados. Tem o direito de obter a confirmação sobre se a SOPAC, S.A. se encontra a proceder ao tratamento dos seus dados pessoais, pelo que tem o direito de aceder aos mesmos, retificando os dados incorretos ou solicitando a sua eliminação quando já não sejam necessários, podendo fazê-lo através do endereço de e-mail protecaodedados@adp-fertilizantes.pt. O conteúdo deste e-mail e respetivos anexos são estritamente confidenciais. Caso não seja o destinatário e tenha recebido esta mensagem por engano, agradeceríamos que informasse imediatamente o remetente, sem divulgar, armazenar ou copiar seu conteúdo. Information is marked as Restricted and belongs to Fertiberia Group Links: ------ [1] https://www.fertiberia.com/pt-pt/adp-fertilizantes/ [2] https://www.linkedin.com/company/fertiberia-s-a/mycompany/ [3] https://twitter.com/grupofertiberia [4] https://www.instagram.com/fertiberia/</v>
+        <v>Prezada Equipe, Devido ao recesso da nossa empresa, as respostas foram lentas. Temos o prazer de informar que nosso cliente confirmou sua proposta e anexamos o novo pedido. Solicitamos que nos enviem a Fatura Proforma para as devidas providências. O departamento de compras cuidará do necessário. Melhores cumprimentos, Tania Raimundo Departamento Comercial +351 926 989 550 Acessórios para a indústria de torneiras LDA. | www.dav.pt [1] Rua das Gramelhas | 13, 4715-431 Braga | Portugal Links: ------ [1] http://www.dav.pt/</v>
       </c>
       <c r="F6" t="str">
-        <v>Pedido de Informação</v>
+        <v>Pedido de Encomenda</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -660,24 +660,24 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/22683.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26007.json</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>22737</v>
+        <v>26016</v>
       </c>
       <c r="B7" t="str">
-        <v>Sat, 29 Mar 2025 12:58:51 -0700</v>
+        <v>Wed, 01 Apr 2026 21:49:27 +0200</v>
       </c>
       <c r="C7" t="str">
-        <v>"angela" &lt;angela@rhernandez.com&gt;</v>
+        <v>"Duane Lucas" &lt;duanelucas@ucsh.com&gt;</v>
       </c>
       <c r="D7" t="str">
-        <v>Nota de Crédito 202503124529.</v>
+        <v>***SPAM***  Solicitação de cotização e confirmação de pedido para consulta nº 1 616195SFMS — Suministro de novo lote (2026)</v>
       </c>
       <c r="E7" t="str">
-        <v>Boa tarde, Serve o presente para enviar a vossa Nota de Crédito assinada e carimbada. Tenho a relembrar que ainda não recebemos a fatura FT 25/0209, correspondente a esta mesma NC Atentamente Andreia Gomes Tlf: 282411120 966204840</v>
+        <v>Bom dia! Aqui é Duane, da UCSH. Temos interesse em seus produtos; portanto, solicitamos que nos envie a melhor oferta para o arquivo anexo, contendo o peso e as dimensões totais, o prazo e o local de entrega. Atenciosamente, Duane Lucas Gerente de Showroom e Desenvolvimento de Negócios | Upper Canada Specialty Hardware E: duanelucas@ucsh.com | P: 905-940-8158 Ext.350 | M: 416-902-3752 | W: www.ucsh.com [1] Links: ------ [1] http://www.ucsh.com/</v>
       </c>
       <c r="F7" t="str">
         <v>Pedido de Informação</v>
@@ -704,24 +704,24 @@
         <v/>
       </c>
       <c r="N7" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/22737.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26016.json</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>24351</v>
+        <v>26054</v>
       </c>
       <c r="B8" t="str">
-        <v>Wed, 01 Oct 2025 08:48:04 +0100</v>
+        <v>Thu, 09 Apr 2026 01:39:12 -0700</v>
       </c>
       <c r="C8" t="str">
-        <v>"GLOBALBRICO Geral" &lt;geral@globalbrico.pt&gt;</v>
+        <v>"Natália Mendes" &lt;info@wememuleovsr.ooguy.com&gt;</v>
       </c>
       <c r="D8" t="str">
-        <v>FW: Consulta de preco AK25/001896 - SW24/413387 para pedido de aquisição de material/artigo QZA na Kremler Landtechnik Compras: [LOTE EXTERNO DE OUTUBRO]</v>
+        <v>Solicitação de Cotação RS0045294, Licitação MR-161127 (Ordem de Projeto: Fornecimento e Entrega - 1328)</v>
       </c>
       <c r="E8" t="str">
-        <v>Com os melhores cumprimentos, De: Sebastiao Monteiro Enviada: 30 de setembro de 2025 18:26 Para: undisclosed-recipients: Assunto: Consulta de preco AK25/001896 - SW24/413387 para pedido de aquisição de material/artigo QZA na Kremler Landtechnik Compras: [LOTE EXTERNO DE OUTUBRO] Bom dia, Precisamos de uma proposta para os itens a seguir listados. Por favor, verifique e responda com o melhor preço com desconto para um pedido imediato. A sua equipa foi recomendada por um parceiro em comum e esperamos finalizar o negócio o mais rapidamente possível. Com os meus respeitosos cumprimentos, Sebastião Monteiro Gomes Reclamos Luminosos Lda Rua do Crasto, 637 Valadares V.N. Gaia 4405-550 Portugal Tel: 227136011/225365361 Fax: 227125081/225365431 sebastiaomonteiro@reclamosferma.com http:/www.reclamosferma.com</v>
+        <v>Bom dia! Por favor, veja o arquivo anexo e responda-nos de acordo com o anexo, enviando a cota&amp;ccedil;&amp;atilde;o. Confirme o recebimento deste e-mail e envie-nos a proposta o mais breve poss&amp;iacute;vel. Para mais informa&amp;ccedil;&amp;otilde;es, consulte o anexo. Obrigada, Cumprimentos / Best Regards / Saludos, Nat&amp;aacute;lia Mendes Accounting Assistant Telefone : 253 410 221 | Chamada para a rede fixa nacional Email: : nataliateixeira@ sartis.pt Tv. da Ribeira n&amp;ordm; 83, 4810-235 Guimar&amp;atilde;es www.sartis.pt</v>
       </c>
       <c r="F8" t="str">
         <v>Pedido de Informação</v>
@@ -748,24 +748,24 @@
         <v/>
       </c>
       <c r="N8" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/24351.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26054.json</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>24501</v>
+        <v>26057</v>
       </c>
       <c r="B9" t="str">
-        <v>Fri, 17 Oct 2025 02:19:50 +0200</v>
+        <v>Thu, 09 Apr 2026 03:00:25 -0700</v>
       </c>
       <c r="C9" t="str">
-        <v>"Kathy Rashid" &lt;kathy@ifzsb.com&gt;</v>
+        <v>"Natália Mendes" &lt;info@wememuleovsr.ooguy.com&gt;</v>
       </c>
       <c r="D9" t="str">
-        <v>***SPAM***  Request for Quotation-RFQ 5387/25_DESB</v>
+        <v>Solicitação de Cotação RS0045294, Licitação MR-161127 (Ordem de Projeto: Fornecimento e Entrega - 1328)</v>
       </c>
       <c r="E9" t="str">
-        <v>Dear Sir / Madam, Attn: Sales Department We need your assistance to _quote for the attached items with your best delivery price._ Also, please include the requirement as per below: 1. Please offer as per the specification given. If offers alternatives, please state the deviations and provide together any technical brochures/specification. 2. Please attach together the CATALOGUE / BROCHURE/ DRAWING for the item. 3. For delivery, please offer your best price and delivery to EX-WORK FACTORY / DDP-PUCHONG,SELANGOR MALAYSIA. 4. Please stated CLEARLY DELIVERY LEAD TIME (DAYS / WEEKS). WE REALLY APPRECIATED IF YOU CAN SEND YOUR QUOTATION ASAP BY 21.10.2025 BEFORE 4.00PM KINDLY PLEASE REPLY THIS EMAIL FOR YOUR ACKNOWLEDGEMENT RECEIPT OF THE ENQUIRY. Should have further clarification, directly can contact undersigned below. Thank you. Regards, Kathy Rashid IFZ OIL &amp; GAS (M) SDN BHD (902524-X) 1-5B, Jalan PP 5C/1, Taman Putra Perdana, 47100 Puchong, Selangor, Malaysia [1] Tel: +603 8318 7010 | Fax: +603 8322 6011| Mobile: +6016 7121907 Email: kathy@ifzsb.com Links: ------ [1] https://www.google.com/maps/search/5C%2F1,+Taman+Putra+Perdana,+47100+Puchong,+Selangor,+Malaysia?entry=gmail&amp;amp;source=g</v>
+        <v>Bom dia! Por favor, veja o arquivo anexo e responda-nos de acordo com o anexo, enviando a cota&amp;ccedil;&amp;atilde;o. Confirme o recebimento deste e-mail e envie-nos a proposta o mais breve poss&amp;iacute;vel. Para mais informa&amp;ccedil;&amp;otilde;es, consulte o anexo. Obrigada, Cumprimentos / Best Regards / Saludos, Nat&amp;aacute;lia Mendes Accounting Assistant Telefone : 253 410 221 | Chamada para a rede fixa nacional Email: : nataliateixeira@ sartis.pt Tv. da Ribeira n&amp;ordm; 83, 4810-235 Guimar&amp;atilde;es www.sartis.pt</v>
       </c>
       <c r="F9" t="str">
         <v>Pedido de Informação</v>
@@ -792,24 +792,24 @@
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/24501.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26057.json</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>25634</v>
+        <v>26505</v>
       </c>
       <c r="B10" t="str">
-        <v>Fri, 20 Feb 2026 13:50:14 +0100</v>
+        <v>Mon, 25 May 2026 11:27:29 +0000</v>
       </c>
       <c r="C10" t="str">
-        <v>"NORMOLDE | Compras" &lt;geral@somax.com.pt&gt;</v>
+        <v>"TAINARA OIL" &lt;info@jujunipiopsa.ooguy.com&gt;</v>
       </c>
       <c r="D10" t="str">
-        <v>Pedido de Cotação nº 20/02/2026</v>
+        <v>Re: Fornecimento ERP 2026100680</v>
       </c>
       <c r="E10" t="str">
-        <v>Boa tarde, Em anexo envio o n/ Pedido de Cotação nº 20/02/2026. Agradecemos a máxima brevidade no envio desta cotação. Obrigada! Cumprimentos, Alexandra Amado NORMOLDE, LDA. Telefone: 244 542652 / Fax: 244 542330 E-mail: compras@normolde.pt web: www.normolde.pt [1] Links: ------ [1] http://www.normolde.pt/</v>
+        <v>Bom dia, Sou Tanari da Logiphorika. Temos um pedido que se enquadra na sua gama de produtos, conforme o arquivo em anexo. Agradecer&amp;iacute;amos muito se pudesse nos fornecer seu pre&amp;ccedil;o competitivo, bem como os dados relevantes. Aguardo sua resposta o mais breve poss&amp;iacute;vel. Atenciosamente, &amp;#1057; &amp;#1091;&amp;#1074;&amp;#1072;&amp;#1078;&amp;#1077;&amp;#1085;&amp;#1080;&amp;#1077;&amp;#1084; | Best regards | Melhores cumprimentos TAINARA OIL Supervisor do Departamento Tel Portugal +351 214 150 244 Portugal +351 966 916 736 Call Angola +244 916 518 828 PROCUREMENT@LOGIPHORIKA.PT Logiphorika Lda NIF 514 046 902 Address: Rua Ant&amp;ocirc;nio Jos&amp;eacute; de Almeida 1A, basement &amp;#8211; back entrance &amp;#8211; 2745-720 Massam&amp;aacute; - Lisbon - PORTUGAL</v>
       </c>
       <c r="F10" t="str">
         <v>Pedido de Informação</v>
@@ -836,27 +836,27 @@
         <v/>
       </c>
       <c r="N10" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/25634.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26505.json</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>25980</v>
+        <v>26666</v>
       </c>
       <c r="B11" t="str">
-        <v>Mon, 30 Mar 2026 11:42:00 +0000</v>
+        <v>Mon, 15 Jun 2026 21:22:01 +1000</v>
       </c>
       <c r="C11" t="str">
-        <v>"Luisr Silva" &lt;luisr.silva@braga.pt&gt;</v>
+        <v>"Denisson Gonçalves" &lt;info@lovsr.ooguy.com&gt;</v>
       </c>
       <c r="D11" t="str">
-        <v>***SPAM***  Genehmigte Projektlieferung für aktuelles Verkaufsangebot: Folgeauftrag zur vorherigen Anfrage (SQ-202604)</v>
+        <v>Solicitação de cotação para artigos/materiais - QME2675079 Entrega: 2026</v>
       </c>
       <c r="E11" t="str">
-        <v>Saudações de Braga, Estamos entrando em contato após nossa conversa telefônica com seu colega sobre o novo pedido. Compilamos uma lista de requisitos que são urgentemente necessários. Por favor, verifique o arquivo anexo para todas as especificações e forneça mais detalhes com os termos de preço para prosseguirmos com o pedido. Atenciosamente, Luís Silva Técnico Superior luisr.silva@braga.pt T: 253 61 60 60 | Ext: 1108 www.braga.pt [1] Este e-mail é amigo do ambiente, pondere antes de o imprimir! CONFIDENCIALIDADE E PRIVACIDADE: Esta mensagem destina-se exclusivamente a quem nela conste como destinatário, contém informação confidencial, encontra-se protegida por segredo profissional e pode conter dados pessoais, sendo a sua divulgação proibida por lei. Caso não seja o destinatário desta mensagem agradecemos que a elimine imediatamente do seu sistema e informe o remetente, via e-mail ou telefone. Para informações sobre as práticas de privacidade do Município de Braga, consulte a Política de Privacidade [2]. Links: ------ [1] http://www.braga.pt/ [2] https://www.cm-braga.pt/pt/0503/politica-de-privacidade</v>
+        <v>Bom dia, Espero que esteja bem. Gostaria de solicitar um or&amp;ccedil;amento hoje, pois &amp;eacute; urgente; tentei entrar em contato por telefone, mas sem sucesso. Por favor, verifique o pedido e responda ainda hoje. Atenciosamente, Denisson Gon&amp;ccedil;alves Comercial AMS Equipamentos Industriais LTDA (31) 99546-2210 commercial@amsequipamentos. com.br</v>
       </c>
       <c r="F11" t="str">
-        <v>Pedido de Informação</v>
+        <v>Pedido de Encomenda</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -880,24 +880,24 @@
         <v/>
       </c>
       <c r="N11" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/25980.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26666.json</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>26004</v>
+        <v>26730</v>
       </c>
       <c r="B12" t="str">
-        <v>Wed, 01 Apr 2026 10:04:22 +0000</v>
+        <v>Mon, 22 Jun 2026 15:51:31 +0000</v>
       </c>
       <c r="C12" t="str">
-        <v>"Raul Figueiredo" &lt;raulfigueiredo@enercon.de&gt;</v>
+        <v>"Ricardo Piedade" &lt;info@hoopzx.ooguy.com&gt;</v>
       </c>
       <c r="D12" t="str">
-        <v>***SPAM***  Verkaufsangebot RFQ-2501524: 04_2026_LPO Lieferung von PROJEKTARTIKELN in großen Mengen</v>
+        <v>***SPAM***  CONSULTA EUROPEIA E261138 (A001)  ESPECIFICAÇÕES DO PRODUTOSERVIÇO</v>
       </c>
       <c r="E12" t="str">
-        <v>Bom dia,, Bom dia, Esta é uma resposta à nossa mensagem anterior, enviada pelo nosso departamento de compras, referente à sua lista de preços e fornecimento. Estamos prontos para prosseguir com o pedido. Todos os detalhes estão no arquivo anexo. Extraia o arquivo para visualizar os detalhes. Por favor, prossiga com a preparação da ordem de compra e confirme se os preços são os mesmos. Aguardamos sua resposta o mais breve possível. Os melhores cumprimentos / Best regards / Mit freundlichen Grüßen Raul Figueiredo Service Operations - Regional Lead Southern Europe &amp; Latin America Mobile : +351 912 746 580 (Quick Dial 2158) mailto : raulfigueiredo@enercon.de</v>
+        <v>Ol&amp;aacute;, Espero que esteja bem. Precisamos urgentemente dos modelos em anexo da sua empresa. Gostaria de solicitar um or&amp;ccedil;amento hoje para dar prosseguimento ao pedido do nosso cliente. Tentamos entrar em contato com sua equipe por telefone, mas n&amp;atilde;o conseguimos. Por favor, confirme a quantidade m&amp;aacute;xima que pode ser fornecida imediatamente. Por favor, analise o pedido e responda ainda hoje. Com os melhores cumprimentos / Saludos cordiales Mit freundlichen Gr&amp;uuml;&amp;szlig;en / With kind regards, Ricardo Piedade T&amp;eacute;cnico-Comercial / Sales Representative Divis&amp;atilde;o Ind&amp;uacute;stria / BA&amp;Uacute; Division F&amp;Ouml;RCH PORTUGAL, Lda &amp;#65279;Centro Empresarial Sintra-Estoril III Rua P&amp;eacute; de Mouro, N&amp;ordm; 33 - Armaz&amp;eacute;m J 2710-335 Sintra - Portugal Tel.: (+351) 211 622 000 Telm. ( +351) 966 682 003 www.forch.pt</v>
       </c>
       <c r="F12" t="str">
         <v>Pedido de Encomenda</v>
@@ -924,27 +924,27 @@
         <v/>
       </c>
       <c r="N12" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26004.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26730.json</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>26007</v>
+        <v>26779</v>
       </c>
       <c r="B13" t="str">
-        <v>Wed, 01 Apr 2026 11:52:27 +0000</v>
+        <v>Mon, 29 Jun 2026 05:40:30 -0500</v>
       </c>
       <c r="C13" t="str">
-        <v>"Tania Raimundo" &lt;taniarai@dav.pt&gt;</v>
+        <v>"Antonio Matos" &lt;antonioquarte@amatos.pt&gt;</v>
       </c>
       <c r="D13" t="str">
-        <v>***SPAM***  Re: Solicitação de Cotação: Confirmação do pedido de consulta - 1- 616195SFMS-2026, Fornecimento de Novo Lote</v>
+        <v>***SPAM***  Envio de recibo REC - REC 11124/8103</v>
       </c>
       <c r="E13" t="str">
-        <v>Prezada Equipe, Devido ao recesso da nossa empresa, as respostas foram lentas. Temos o prazer de informar que nosso cliente confirmou sua proposta e anexamos o novo pedido. Solicitamos que nos enviem a Fatura Proforma para as devidas providências. O departamento de compras cuidará do necessário. Melhores cumprimentos, Tania Raimundo Departamento Comercial +351 926 989 550 Acessórios para a indústria de torneiras LDA. | www.dav.pt [1] Rua das Gramelhas | 13, 4715-431 Braga | Portugal Links: ------ [1] http://www.dav.pt/</v>
+        <v>Caro Cliente, Junto enviamos Documento de Liquida&amp;ccedil;&amp;atilde;o REC emitido em 25-06-26 no valor de 2314,54 euros. Nota: Este mail foi enviado por um processo autom&amp;aacute;tico. Por favor n&amp;atilde;o responder para este endere&amp;ccedil;o. Cumprimentos, Antonio Matos, Lda Rua da Almagreira, 167 4910-354 Venade</v>
       </c>
       <c r="F13" t="str">
-        <v>Pedido de Encomenda</v>
+        <v>SPAM</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -968,24 +968,24 @@
         <v/>
       </c>
       <c r="N13" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26007.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26779.json</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>26016</v>
+        <v>26995</v>
       </c>
       <c r="B14" t="str">
-        <v>Wed, 01 Apr 2026 21:49:27 +0200</v>
+        <v>Mon, 20 Jul 2026 11:34:35 +0000</v>
       </c>
       <c r="C14" t="str">
-        <v>"Duane Lucas" &lt;duanelucas@ucsh.com&gt;</v>
+        <v>"Da Silva" &lt;info@dalidioman.ooguy.com&gt;</v>
       </c>
       <c r="D14" t="str">
-        <v>***SPAM***  Solicitação de cotização e confirmação de pedido para consulta nº 1 616195SFMS — Suministro de novo lote (2026)</v>
+        <v>Finalização do Pedido de Fornecimento – Referência de Lote: H80-26-0155 – Apresentação de Preços e Confirmação de Especificações.</v>
       </c>
       <c r="E14" t="str">
-        <v>Bom dia! Aqui é Duane, da UCSH. Temos interesse em seus produtos; portanto, solicitamos que nos envie a melhor oferta para o arquivo anexo, contendo o peso e as dimensões totais, o prazo e o local de entrega. Atenciosamente, Duane Lucas Gerente de Showroom e Desenvolvimento de Negócios | Upper Canada Specialty Hardware E: duanelucas@ucsh.com | P: 905-940-8158 Ext.350 | M: 416-902-3752 | W: www.ucsh.com [1] Links: ------ [1] http://www.ucsh.com/</v>
+        <v>Ol&amp;aacute;, Sou Da Silva e entro em contato em nome da nossaexport.com. Temos interesse em seus produtos e em sua expertise. Este &amp;eacute; o nosso primeiro contato oficial e buscamos estabelecer uma parceria comercial s&amp;oacute;lida e de longo prazo com voc&amp;ecirc;s. Analisamos o site de voc&amp;ecirc;s e solicitamos, por meio desta, pre&amp;ccedil;os com desconto para os itens listados no arquivo em anexo, a fim de realizarmos um pedido em grande quantidade o mais breve poss&amp;iacute;vel. Al&amp;eacute;m disso, gostar&amp;iacute;amos de falar diretamente com o departamento de vendas para cadastrar sua equipe em nosso sistema e enviar nosso pedido de compra assim que recebermos seu retorno. Se poss&amp;iacute;vel, tamb&amp;eacute;m gostar&amp;iacute;amos de agendar uma reuni&amp;atilde;o com sua equipe ap&amp;oacute;s o envio do pedido de compra para discutirmos melhor nossas necessidades. Por favor, verifique o arquivo com todas as especifica&amp;ccedil;&amp;otilde;es. Aguardamos seu retorno ainda hoje. Kind regards | Com os melhores cumprimentos, Domingos Da Silva Assistente Comercial NIF: 5002151367 NOSSAEXPORT-BRASIL www.nossaexport.com +55 (48) 99196-6411 commercial@nossaexport.com</v>
       </c>
       <c r="F14" t="str">
         <v>Pedido de Informação</v>
@@ -1012,27 +1012,27 @@
         <v/>
       </c>
       <c r="N14" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26016.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26995.json</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>26054</v>
+        <v>27009</v>
       </c>
       <c r="B15" t="str">
-        <v>Thu, 09 Apr 2026 01:39:12 -0700</v>
+        <v>Tue, 21 Jul 2026 11:57:38 +0000</v>
       </c>
       <c r="C15" t="str">
-        <v>"Natália Mendes" &lt;info@wememuleovsr.ooguy.com&gt;</v>
+        <v>"alertas.empresas.millenniumbcp.pt" &lt;alertas.empresas.millenniumbcp.pt@tardio.info&gt;</v>
       </c>
       <c r="D15" t="str">
-        <v>Solicitação de Cotação RS0045294, Licitação MR-161127 (Ordem de Projeto: Fornecimento e Entrega - 1328)</v>
+        <v>Documentos em formato digital</v>
       </c>
       <c r="E15" t="str">
-        <v>Bom dia! Por favor, veja o arquivo anexo e responda-nos de acordo com o anexo, enviando a cota&amp;ccedil;&amp;atilde;o. Confirme o recebimento deste e-mail e envie-nos a proposta o mais breve poss&amp;iacute;vel. Para mais informa&amp;ccedil;&amp;otilde;es, consulte o anexo. Obrigada, Cumprimentos / Best Regards / Saludos, Nat&amp;aacute;lia Mendes Accounting Assistant Telefone : 253 410 221 | Chamada para a rede fixa nacional Email: : nataliateixeira@ sartis.pt Tv. da Ribeira n&amp;ordm; 83, 4810-235 Guimar&amp;atilde;es www.sartis.pt</v>
+        <v>Estimado(a) Cliente, Enviamos o documento em formato digital (.pdf): Documentos em formato digital do movimento feito na conta 45556587090 para que possa consultar de forma r&amp;aacute;pida e c&amp;oacute;moda. No site, basta fazer login e ir a "Opera&amp;ccedil;&amp;otilde;es Banc&amp;aacute;rias &gt; Outros Servi&amp;ccedil;os &gt; Documentos &gt; Notas de Lan&amp;ccedil;amento" para ter acesso aos documentos emitidos nos &amp;uacute;ltimos 12 meses. Caso pretenda receb&amp;ecirc;-lo noutro email, aceda a "Alertas &gt; Notas de Lan&amp;ccedil;amento" e, na op&amp;ccedil;&amp;atilde;o "Criar Novo", indique o novo endere&amp;ccedil;o. J&amp;Aacute; CONHECE A APP M EMPRESAS ? Instale j&amp;aacute; e fa&amp;ccedil;a a gest&amp;atilde;o da sua Empresa a partir do smartphone. Simples, r&amp;aacute;pida e intuitiva! Com os melhores cumprimentos, millenniumbcp.pt Este e-mail &amp;eacute; apenas informativo, n&amp;atilde;o responda a este endere&amp;ccedil;o. Estes e-mails n&amp;atilde;o permitem o acesso direto ao Site do Millennium bcp, n&amp;atilde;o incluem atalhos (links)* nem s&amp;atilde;o utilizados para solicitar quaisquer elementos identificativos ou c&amp;oacute;digos de acesso. Se n&amp;atilde;o pretende receber e-mails do tema em ep&amp;iacute;grafe, envie um e-mail para a caixa: extratodigital.remover.campanhas@millenniumbcp.pt com o assunto "Remover". Se n&amp;atilde;o pretende receber mais e-mails publicit&amp;aacute;rios do Millennium bcp, envie um e-mail para a caixa: tudo.remover.campanhas@millenniumbcp.pt com o assunto "Remover tudo". Banco Comercial Portugu&amp;ecirc;s, S.A., registado no Banco de Portugal sob o n&amp;ordm;. 33; Sede: Pra&amp;ccedil;a D. Jo&amp;atilde;o I, 28, 4000-295 Porto; Capital Social: 3.000.000.000 euros; N&amp;uacute;mero &amp;uacute;nico de matr&amp;iacute;cula e de identifica&amp;ccedil;&amp;atilde;o fiscal: 501525882 (Conservat&amp;oacute;ria do Registo Comercial do Porto). *Alguns servi&amp;ccedil;os de e-mail assumem, automaticamente, links em certas palavras, sem qualquer responsabilidade por parte do Millennium bcp. 91 850 45 04 &amp;bull; 93 050 45 04 &amp;bull; 96 150 41 26 (chamada para rede m&amp;oacute;vel nacional) +351 21 004 24 24 (chamada para rede fixa nacional) Dispon&amp;iacute;vel todos os dias das 08h &amp;agrave;s 22h, hora de Portugal Continental. O custo das comunica&amp;ccedil;&amp;otilde;es depende do tarif&amp;aacute;rio acordado com o seu operador.</v>
       </c>
       <c r="F15" t="str">
-        <v>Pedido de Informação</v>
+        <v>SPAM</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1056,27 +1056,27 @@
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26054.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27009.json</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>26057</v>
+        <v>27018</v>
       </c>
       <c r="B16" t="str">
-        <v>Thu, 09 Apr 2026 03:00:25 -0700</v>
+        <v>Wed, 22 Jul 2026 07:11:13 +0000</v>
       </c>
       <c r="C16" t="str">
-        <v>"Natália Mendes" &lt;info@wememuleovsr.ooguy.com&gt;</v>
+        <v>"alertas.empresas.millenniumbcp.pt" &lt;alertas.empresas.millenniumbcp.pt@cansidro.info&gt;</v>
       </c>
       <c r="D16" t="str">
-        <v>Solicitação de Cotação RS0045294, Licitação MR-161127 (Ordem de Projeto: Fornecimento e Entrega - 1328)</v>
+        <v>Documentos em formato digital</v>
       </c>
       <c r="E16" t="str">
-        <v>Bom dia! Por favor, veja o arquivo anexo e responda-nos de acordo com o anexo, enviando a cota&amp;ccedil;&amp;atilde;o. Confirme o recebimento deste e-mail e envie-nos a proposta o mais breve poss&amp;iacute;vel. Para mais informa&amp;ccedil;&amp;otilde;es, consulte o anexo. Obrigada, Cumprimentos / Best Regards / Saludos, Nat&amp;aacute;lia Mendes Accounting Assistant Telefone : 253 410 221 | Chamada para a rede fixa nacional Email: : nataliateixeira@ sartis.pt Tv. da Ribeira n&amp;ordm; 83, 4810-235 Guimar&amp;atilde;es www.sartis.pt</v>
+        <v>Estimado(a) Cliente, Enviamos o documento em formato digital (.pdf): Documentos em formato digital do movimento feito na conta 45556587090 para que possa consultar de forma r&amp;aacute;pida e c&amp;oacute;moda. No site, basta fazer login e ir a "Opera&amp;ccedil;&amp;otilde;es Banc&amp;aacute;rias &gt; Outros Servi&amp;ccedil;os &gt; Documentos &gt; Notas de Lan&amp;ccedil;amento" para ter acesso aos documentos emitidos nos &amp;uacute;ltimos 12 meses. Caso pretenda receb&amp;ecirc;-lo noutro email, aceda a "Alertas &gt; Notas de Lan&amp;ccedil;amento" e, na op&amp;ccedil;&amp;atilde;o "Criar Novo", indique o novo endere&amp;ccedil;o. J&amp;Aacute; CONHECE A APP M EMPRESAS ? Instale j&amp;aacute; e fa&amp;ccedil;a a gest&amp;atilde;o da sua Empresa a partir do smartphone. Simples, r&amp;aacute;pida e intuitiva! Com os melhores cumprimentos, millenniumbcp.pt Este e-mail &amp;eacute; apenas informativo, n&amp;atilde;o responda a este endere&amp;ccedil;o. Estes e-mails n&amp;atilde;o permitem o acesso direto ao Site do Millennium bcp, n&amp;atilde;o incluem atalhos (links)* nem s&amp;atilde;o utilizados para solicitar quaisquer elementos identificativos ou c&amp;oacute;digos de acesso. Se n&amp;atilde;o pretende receber e-mails do tema em ep&amp;iacute;grafe, envie um e-mail para a caixa: extratodigital.remover.campanhas@millenniumbcp.pt com o assunto "Remover". Se n&amp;atilde;o pretende receber mais e-mails publicit&amp;aacute;rios do Millennium bcp, envie um e-mail para a caixa: tudo.remover.campanhas@millenniumbcp.pt com o assunto "Remover tudo". Banco Comercial Portugu&amp;ecirc;s, S.A., registado no Banco de Portugal sob o n&amp;ordm;. 33; Sede: Pra&amp;ccedil;a D. Jo&amp;atilde;o I, 28, 4000-295 Porto; Capital Social: 3.000.000.000 euros; N&amp;uacute;mero &amp;uacute;nico de matr&amp;iacute;cula e de identifica&amp;ccedil;&amp;atilde;o fiscal: 501525882 (Conservat&amp;oacute;ria do Registo Comercial do Porto). *Alguns servi&amp;ccedil;os de e-mail assumem, automaticamente, links em certas palavras, sem qualquer responsabilidade por parte do Millennium bcp. 91 850 45 04 &amp;bull; 93 050 45 04 &amp;bull; 96 150 41 26 (chamada para rede m&amp;oacute;vel nacional) +351 21 004 24 24 (chamada para rede fixa nacional) Dispon&amp;iacute;vel todos os dias das 08h &amp;agrave;s 22h, hora de Portugal Continental. O custo das comunica&amp;ccedil;&amp;otilde;es depende do tarif&amp;aacute;rio acordado com o seu operador.</v>
       </c>
       <c r="F16" t="str">
-        <v>Pedido de Informação</v>
+        <v>SPAM</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1100,24 +1100,24 @@
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26057.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27018.json</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>26505</v>
+        <v>27182</v>
       </c>
       <c r="B17" t="str">
-        <v>Mon, 25 May 2026 11:27:29 +0000</v>
+        <v>Tue, 11 Aug 2026 15:53:55 +0000</v>
       </c>
       <c r="C17" t="str">
-        <v>"TAINARA OIL" &lt;info@jujunipiopsa.ooguy.com&gt;</v>
+        <v>"karla" &lt;info@retesp.com&gt;</v>
       </c>
       <c r="D17" t="str">
-        <v>Re: Fornecimento ERP 2026100680</v>
+        <v>Solicitação de Cotação e Especificações do Pedido – Agosto de 2026</v>
       </c>
       <c r="E17" t="str">
-        <v>Bom dia, Sou Tanari da Logiphorika. Temos um pedido que se enquadra na sua gama de produtos, conforme o arquivo em anexo. Agradecer&amp;iacute;amos muito se pudesse nos fornecer seu pre&amp;ccedil;o competitivo, bem como os dados relevantes. Aguardo sua resposta o mais breve poss&amp;iacute;vel. Atenciosamente, &amp;#1057; &amp;#1091;&amp;#1074;&amp;#1072;&amp;#1078;&amp;#1077;&amp;#1085;&amp;#1080;&amp;#1077;&amp;#1084; | Best regards | Melhores cumprimentos TAINARA OIL Supervisor do Departamento Tel Portugal +351 214 150 244 Portugal +351 966 916 736 Call Angola +244 916 518 828 PROCUREMENT@LOGIPHORIKA.PT Logiphorika Lda NIF 514 046 902 Address: Rua Ant&amp;ocirc;nio Jos&amp;eacute; de Almeida 1A, basement &amp;#8211; back entrance &amp;#8211; 2745-720 Massam&amp;aacute; - Lisbon - PORTUGAL</v>
+        <v>Prezada Equipe, Espero que estejam bem. Poderiam, por favor, compartilhar o preço, o prazo de entrega e os requisitos para os seguintes modelos de produto, com base no documento anexo? Agradeceríamos o envio de sua cotação assim que possível. Atenciosamente, _Melhores cumprimentos / Saludos / Best Regards_ _ _ _"Jesus é a nossa Bandeira de Vitória!" "¡Jesús es nuestra Bandera de la Victoria!"_ _ "Jesus is our Banner of Victory!"_ _ ​_ ​</v>
       </c>
       <c r="F17" t="str">
         <v>Pedido de Informação</v>
@@ -1144,27 +1144,27 @@
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26505.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27182.json</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>26591</v>
+        <v>27453</v>
       </c>
       <c r="B18" t="str">
-        <v>Mon, 01 Jun 2026 15:54:50 +0200</v>
+        <v>Thu, 17 Sep 2026 16:54:30 +0100</v>
       </c>
       <c r="C18" t="str">
-        <v>"Jorge Miguel" &lt;italfrombrands@italfrom.com&gt;</v>
+        <v>"Pedro - Cardoso Leal" &lt;pedro@cardosoleal.com&gt;</v>
       </c>
       <c r="D18" t="str">
-        <v>Pedido de Cotação-20260601</v>
+        <v>Encomenda - CARDOSO LEAL</v>
       </c>
       <c r="E18" t="str">
-        <v>Boa tarde, Em anexo o n/ped. de cotação 010626, agradeço resposta antes de 05/06/2026. * Mencionar o n/nº de consulta * Indicar o prazo de entrega Jorge Miguel Reis Armazém / Aprovisionamentos miguelreis@sopac.pt + 351 265 030 498 Rua do Rio Mondego Parque Ind. Sapec-Bay 2910-543 Setúbal fertiberia.com/adp-fertilizantes/ [1] [2] [3] [4] De acordo com a legislação em vigor em matéria de Proteção de Dados Pessoais, informamos que os dados pessoais contidos nesta comunicação estão incorporados num ficheiro cujo responsável é a SOPAC, S.A., cuja finalidade é o correto desenvolvimento das relações comerciais, profissionais e/ou de negócio; apenas serão cedidos a empresas do grupo com a mesma finalidade, não serão cedidos ou transmitidos a terceiros, salvo obrigação legal, e serão conservados enquanto não for solicitada a sua eliminação. Informamos, ainda, que a SOPAC, S.A. adotou as medidas de segurança adequadas nas suas instalações, sistemas, tratamentos e arquivos, garantindo a confidencialidade dos seus dados. Tem o direito de obter a confirmação sobre se a SOPAC, S.A. se encontra a proceder ao tratamento dos seus dados pessoais, pelo que tem o direito de aceder aos mesmos, retificando os dados incorretos ou solicitando a sua eliminação quando já não sejam necessários, podendo fazê-lo através do endereço de e-mail protecaodedados@adp-fertilizantes.pt. O conteúdo deste e-mail e respetivos anexos são estritamente confidenciais. Caso não seja o destinatário e tenha recebido esta mensagem por engano, agradeceríamos que informasse imediatamente o remetente, sem divulgar, armazenar ou copiar seu conteúdo. Links: ------ [1] https://www.fertiberia.com/pt-pt/adp-fertilizantes/ [2] https://www.linkedin.com/company/fertiberia-s-a/mycompany/ [3] https://twitter.com/grupofertiberia [4] https://www.instagram.com/fertiberia/</v>
+        <v>Boa tarde, Envio em anexo a seguinte encomenda. Alguma dúvida não hesite em nos contactar. Os melhores cumprimentos / Cordialement / Best Regards, Pedro Cardoso Leal Rua Stª. Marinha - nº 53 | 4595-349 Penamaior | Paços de Ferreira | Tel: +351-255 891 587 | www.cardosoleal.com</v>
       </c>
       <c r="F18" t="str">
-        <v>Pedido de Informação</v>
+        <v>Pedido de Encomenda</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1188,27 +1188,27 @@
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26591.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27453.json</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>26666</v>
+        <v>27455</v>
       </c>
       <c r="B19" t="str">
-        <v>Mon, 15 Jun 2026 21:22:01 +1000</v>
+        <v>Thu, 17 Sep 2026 17:47:41 +0000</v>
       </c>
       <c r="C19" t="str">
-        <v>"Denisson Gonçalves" &lt;info@lovsr.ooguy.com&gt;</v>
+        <v>"Jorge Carvalho Fibrosom" &lt;jorge.carvalho@fibrosom.com&gt;</v>
       </c>
       <c r="D19" t="str">
-        <v>Solicitação de cotação para artigos/materiais - QME2675079 Entrega: 2026</v>
+        <v>Proposta Fibrosom</v>
       </c>
       <c r="E19" t="str">
-        <v>Bom dia, Espero que esteja bem. Gostaria de solicitar um or&amp;ccedil;amento hoje, pois &amp;eacute; urgente; tentei entrar em contato por telefone, mas sem sucesso. Por favor, verifique o pedido e responda ainda hoje. Atenciosamente, Denisson Gon&amp;ccedil;alves Comercial AMS Equipamentos Industriais LTDA (31) 99546-2210 commercial@amsequipamentos. com.br</v>
+        <v>Boa tarde, Conforme solicitado envio proposta em anexo. Enviado de Outlook para Android</v>
       </c>
       <c r="F19" t="str">
-        <v>Pedido de Encomenda</v>
+        <v>SPAM</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1219,12 +1219,6 @@
       <c r="I19" t="str">
         <v/>
       </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
       <c r="L19" t="str">
         <v>0</v>
       </c>
@@ -1232,27 +1226,27 @@
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26666.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27455.json</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>26730</v>
+        <v>27459</v>
       </c>
       <c r="B20" t="str">
-        <v>Mon, 22 Jun 2026 15:51:31 +0000</v>
+        <v>Fri, 18 Sep 2026 09:34:31 +0000</v>
       </c>
       <c r="C20" t="str">
-        <v>"Ricardo Piedade" &lt;info@hoopzx.ooguy.com&gt;</v>
+        <v>"Márcia Costa" &lt;marcia.costa@cm-pacosdeferreira.pt&gt;</v>
       </c>
       <c r="D20" t="str">
-        <v>***SPAM***  CONSULTA EUROPEIA E261138 (A001)  ESPECIFICAÇÕES DO PRODUTOSERVIÇO</v>
+        <v>Pedido de orçamento N.º 488</v>
       </c>
       <c r="E20" t="str">
-        <v>Ol&amp;aacute;, Espero que esteja bem. Precisamos urgentemente dos modelos em anexo da sua empresa. Gostaria de solicitar um or&amp;ccedil;amento hoje para dar prosseguimento ao pedido do nosso cliente. Tentamos entrar em contato com sua equipe por telefone, mas n&amp;atilde;o conseguimos. Por favor, confirme a quantidade m&amp;aacute;xima que pode ser fornecida imediatamente. Por favor, analise o pedido e responda ainda hoje. Com os melhores cumprimentos / Saludos cordiales Mit freundlichen Gr&amp;uuml;&amp;szlig;en / With kind regards, Ricardo Piedade T&amp;eacute;cnico-Comercial / Sales Representative Divis&amp;atilde;o Ind&amp;uacute;stria / BA&amp;Uacute; Division F&amp;Ouml;RCH PORTUGAL, Lda &amp;#65279;Centro Empresarial Sintra-Estoril III Rua P&amp;eacute; de Mouro, N&amp;ordm; 33 - Armaz&amp;eacute;m J 2710-335 Sintra - Portugal Tel.: (+351) 211 622 000 Telm. ( +351) 966 682 003 www.forch.pt</v>
+        <v>Exmo. Senhor(a), Vimos por este meio solicitar envio da V/melhor proposta de orçamento, para o que passamos a especificar: 8 Unidades - Cimento Cola Weber-col Classic Branco-25kg 200 KG - Cimento cola cinzento -&gt;Com entrega incluída nas Oficinas Municipais: Rua Joaquim Martins, nº 78 - 4595-242 Meixomil; -&gt; IMPORTANTE: indicar o prazo de entrega em caso de adjudicação; -&gt;Aguardamos propostas até às 17H00 do dia 21-09-2026. Informações importantes para admissão das propostas: - Apenas serão admitidos orçamentos rececionados dentro da data estipulada e para o seguinte email: gabinetedecompras@cm-pacosdeferreira.pt com a indicação dos prazos de entrega e fichas técnicas dos materiais que propuserem (quando aplicável). Devem ainda indicar sempre o nosso número de pedido de orçamento; - Para obter informações sobre adjudicação do procedimento em causa, entrar em contacto com o gabinete de compras, através do contacto de email gabinetedecompras@cm-pacosdeferreira.pt ou telefone 255 860 781, indicando sempre o n.º do respetivo pedido de orçamento. Solicita-se que apenas o façam cerca de duas semanas após data de término para receção de propostas. Informações importantes em caso de adjudicação: - Para pagamento (ENTRE 30 a 60 DIAS após receção de fatura ou conforme acordado, após boa receção dos bens/serviços) é necessário ceder autorização de consulta online das Certidões de Nao Dívida às Finanças e à Segurança Social, indicando o v/ NISS. O NISS do município é: 20003548855. Em caso de não cederem autorização o envio deverá ser feito para os email: geral@cm-pacosdeferreira.pt ou paula.leao@cm-pacosdeferreira.pt ; - É obrigatória a identificação do n.º requisição na própria fatura sob pena de devolução da mesma; - OBRIGATORIEDADE DE EMISSÃO DE FATURA ELETRÓNICA PREVISTA NO ARTIGO 299º - B DO CÓDIGO DOS CONTRATOS PÚBLICOS, os fornecedores da Administração Pública são obrigados a emitir faturas eletrónicas no âmbito da execução de contratos públicos, conforme o disposto no artigo 299. ºB do Código dos Contratos Público (CCP); Faturação Eletrónica, no âmbito da contratação pública (art.º 299-B) Formatos aceites Métodos de envio Faturas em formato PDF geral@cm-pacosdeferreira.pt paula.leao@cm-pacosdeferreira.pt Faturas em formato impresso (papel) Via Correio postal endereçado ao Município PF Faturação eletrónica Através de solução EDI (XML) - Broker YET * (*) O processo de EDI efetua-se através do envio para, faturacao.eletronica@cm-pacosdeferreira.pt , do ficheiro XML, CIUS-PT acompanhado de um PDF com a imagem da fatura que deverá ser certificada digitalmente. O ficheiro XML terá de ter obrigatoriamente os dados que devem constar da fatura, incluindo o número de compromisso. O Município valida este número e a fatura não será aceite se o mesmo for inválido.Em caso de dúvida, deverá contactar os serviços de contabilidade do Município. O nosso prestador de serviços (Broker) é YET - Your Electronic Transactions. Certos da melhor atenção para o exposto e na expectativa de notícias positivas da V/parte, subscrevemo-nos, Melhores cumprimentos Márcia Veiga Gabinete de Compras Contacto Direto: 255 860 781 [cid:cmpf.png]</v>
       </c>
       <c r="F20" t="str">
-        <v>Pedido de Encomenda</v>
+        <v>Pedido de Informação</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1263,12 +1257,6 @@
       <c r="I20" t="str">
         <v/>
       </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
       <c r="L20" t="str">
         <v>0</v>
       </c>
@@ -1276,27 +1264,27 @@
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26730.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27459.json</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>26779</v>
+        <v>27460</v>
       </c>
       <c r="B21" t="str">
-        <v>Mon, 29 Jun 2026 05:40:30 -0500</v>
+        <v>Fri, 18 Sep 2026 11:07:48 +0100</v>
       </c>
       <c r="C21" t="str">
-        <v>"Antonio Matos" &lt;antonioquarte@amatos.pt&gt;</v>
+        <v>miguel.silva@zegnea.com</v>
       </c>
       <c r="D21" t="str">
-        <v>***SPAM***  Envio de recibo REC - REC 11124/8103</v>
+        <v>Pedido de cotação</v>
       </c>
       <c r="E21" t="str">
-        <v>Caro Cliente, Junto enviamos Documento de Liquida&amp;ccedil;&amp;atilde;o REC emitido em 25-06-26 no valor de 2314,54 euros. Nota: Este mail foi enviado por um processo autom&amp;aacute;tico. Por favor n&amp;atilde;o responder para este endere&amp;ccedil;o. Cumprimentos, Antonio Matos, Lda Rua da Almagreira, 167 4910-354 Venade</v>
+        <v>Bom dia, Solicito, por favor, a cotação para o fornecimento de 5 un. de Sika® Separol® Universal, 25 L. A cotação deverá ser efetuada com o NIF 502 753 420 e a entrega na seguinte morada: Rua de Santa Eulália, n.º 387  Tabuadelo 4835-458 Tabuadelo  Guimarães Obrigado. Cumprimentos, Miguel Silva Departamento de Compras Tel.: 918086009 Travessa João de Oliveira Salgado, 32, Costa 4810-015 Guimarães Telf. 253 565 098 (chamada para rede fixa nacional)</v>
       </c>
       <c r="F21" t="str">
-        <v>SPAM</v>
+        <v>Pedido de Informação</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1307,12 +1295,6 @@
       <c r="I21" t="str">
         <v/>
       </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
       <c r="L21" t="str">
         <v>0</v>
       </c>
@@ -1320,27 +1302,27 @@
         <v/>
       </c>
       <c r="N21" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26779.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27460.json</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>26995</v>
+        <v>27462</v>
       </c>
       <c r="B22" t="str">
-        <v>Mon, 20 Jul 2026 11:34:35 +0000</v>
+        <v>Fri, 18 Sep 2026 14:39:43 +0000</v>
       </c>
       <c r="C22" t="str">
-        <v>"Da Silva" &lt;info@dalidioman.ooguy.com&gt;</v>
+        <v>"Cristina Pacheco" &lt;cristina.pacheco@ada.pt&gt;</v>
       </c>
       <c r="D22" t="str">
-        <v>Finalização do Pedido de Fornecimento – Referência de Lote: H80-26-0155 – Apresentação de Preços e Confirmação de Especificações.</v>
+        <v>Encomenda CP260918</v>
       </c>
       <c r="E22" t="str">
-        <v>Ol&amp;aacute;, Sou Da Silva e entro em contato em nome da nossaexport.com. Temos interesse em seus produtos e em sua expertise. Este &amp;eacute; o nosso primeiro contato oficial e buscamos estabelecer uma parceria comercial s&amp;oacute;lida e de longo prazo com voc&amp;ecirc;s. Analisamos o site de voc&amp;ecirc;s e solicitamos, por meio desta, pre&amp;ccedil;os com desconto para os itens listados no arquivo em anexo, a fim de realizarmos um pedido em grande quantidade o mais breve poss&amp;iacute;vel. Al&amp;eacute;m disso, gostar&amp;iacute;amos de falar diretamente com o departamento de vendas para cadastrar sua equipe em nosso sistema e enviar nosso pedido de compra assim que recebermos seu retorno. Se poss&amp;iacute;vel, tamb&amp;eacute;m gostar&amp;iacute;amos de agendar uma reuni&amp;atilde;o com sua equipe ap&amp;oacute;s o envio do pedido de compra para discutirmos melhor nossas necessidades. Por favor, verifique o arquivo com todas as especifica&amp;ccedil;&amp;otilde;es. Aguardamos seu retorno ainda hoje. Kind regards | Com os melhores cumprimentos, Domingos Da Silva Assistente Comercial NIF: 5002151367 NOSSAEXPORT-BRASIL www.nossaexport.com +55 (48) 99196-6411 commercial@nossaexport.com</v>
+        <v>Boa tarde, Encomendo seguinte material, mas preciso que me informem se posso recolher na 2ª feira logo pela manhã: 4 caixas cola e veda branca soudal, igual á última compra. 2 latas tela líquida cinza 4un tubos cola e veda alta temperatura. Com os melhores cumprimentos, Best Regards, CRISTINA PACHECO Purchase Department| Dep. Compras +351 924 489 683 [Descrição: Descrição: cid:image003.png@01D53B36.F5D57EE0]</v>
       </c>
       <c r="F22" t="str">
-        <v>Pedido de Informação</v>
+        <v>Pedido de Encomenda</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1351,12 +1333,6 @@
       <c r="I22" t="str">
         <v/>
       </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
       <c r="L22" t="str">
         <v>0</v>
       </c>
@@ -1364,24 +1340,24 @@
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/26995.json</v>
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27462.json</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>27009</v>
+        <v>27464</v>
       </c>
       <c r="B23" t="str">
-        <v>Tue, 21 Jul 2026 11:57:38 +0000</v>
+        <v>Sat, 19 Sep 2026 20:27:54 +0800</v>
       </c>
       <c r="C23" t="str">
-        <v>"alertas.empresas.millenniumbcp.pt" &lt;alertas.empresas.millenniumbcp.pt@tardio.info&gt;</v>
+        <v>"MAY" &lt;may@directfactorysp.com&gt;</v>
       </c>
       <c r="D23" t="str">
-        <v>Documentos em formato digital</v>
+        <v>***SPAM***  Advanced Magnetic Components for Your Designs</v>
       </c>
       <c r="E23" t="str">
-        <v>Estimado(a) Cliente, Enviamos o documento em formato digital (.pdf): Documentos em formato digital do movimento feito na conta 45556587090 para que possa consultar de forma r&amp;aacute;pida e c&amp;oacute;moda. No site, basta fazer login e ir a "Opera&amp;ccedil;&amp;otilde;es Banc&amp;aacute;rias &gt; Outros Servi&amp;ccedil;os &gt; Documentos &gt; Notas de Lan&amp;ccedil;amento" para ter acesso aos documentos emitidos nos &amp;uacute;ltimos 12 meses. Caso pretenda receb&amp;ecirc;-lo noutro email, aceda a "Alertas &gt; Notas de Lan&amp;ccedil;amento" e, na op&amp;ccedil;&amp;atilde;o "Criar Novo", indique o novo endere&amp;ccedil;o. J&amp;Aacute; CONHECE A APP M EMPRESAS ? Instale j&amp;aacute; e fa&amp;ccedil;a a gest&amp;atilde;o da sua Empresa a partir do smartphone. Simples, r&amp;aacute;pida e intuitiva! Com os melhores cumprimentos, millenniumbcp.pt Este e-mail &amp;eacute; apenas informativo, n&amp;atilde;o responda a este endere&amp;ccedil;o. Estes e-mails n&amp;atilde;o permitem o acesso direto ao Site do Millennium bcp, n&amp;atilde;o incluem atalhos (links)* nem s&amp;atilde;o utilizados para solicitar quaisquer elementos identificativos ou c&amp;oacute;digos de acesso. Se n&amp;atilde;o pretende receber e-mails do tema em ep&amp;iacute;grafe, envie um e-mail para a caixa: extratodigital.remover.campanhas@millenniumbcp.pt com o assunto "Remover". Se n&amp;atilde;o pretende receber mais e-mails publicit&amp;aacute;rios do Millennium bcp, envie um e-mail para a caixa: tudo.remover.campanhas@millenniumbcp.pt com o assunto "Remover tudo". Banco Comercial Portugu&amp;ecirc;s, S.A., registado no Banco de Portugal sob o n&amp;ordm;. 33; Sede: Pra&amp;ccedil;a D. Jo&amp;atilde;o I, 28, 4000-295 Porto; Capital Social: 3.000.000.000 euros; N&amp;uacute;mero &amp;uacute;nico de matr&amp;iacute;cula e de identifica&amp;ccedil;&amp;atilde;o fiscal: 501525882 (Conservat&amp;oacute;ria do Registo Comercial do Porto). *Alguns servi&amp;ccedil;os de e-mail assumem, automaticamente, links em certas palavras, sem qualquer responsabilidade por parte do Millennium bcp. 91 850 45 04 &amp;bull; 93 050 45 04 &amp;bull; 96 150 41 26 (chamada para rede m&amp;oacute;vel nacional) +351 21 004 24 24 (chamada para rede fixa nacional) Dispon&amp;iacute;vel todos os dias das 08h &amp;agrave;s 22h, hora de Portugal Continental. O custo das comunica&amp;ccedil;&amp;otilde;es depende do tarif&amp;aacute;rio acordado com o seu operador.</v>
+        <v>Hi Encomendas, I hope this message finds you well. Further to our previous discussion on power supplies, I wanted to introduce the extensive line of Magnetic Components. These components are critical for ensuring efficiency and compliance in modern electronics. The High Current Power Inductors are a prime example of the innovation available: Engineered with flat wire and powder molding for high performance. Achieve high saturation currents up to 150Amps with low core losses. Magnetically shielded designs to minimize acoustic noise and interference, with AEC-Q200 qualified options. These components are designed to provide a competitive advantage in both performance and cost. Would a sample of our High Current Power Inductors be helpful for your team's evaluation? May Sales Manager K-well Tech If you don't want to receive our emails, you can easily unsubscribe here.</v>
       </c>
       <c r="F23" t="str">
         <v>SPAM</v>
@@ -1395,12 +1371,6 @@
       <c r="I23" t="str">
         <v/>
       </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
       <c r="L23" t="str">
         <v>0</v>
       </c>
@@ -1408,618 +1378,12 @@
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27009.json</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>27018</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Wed, 22 Jul 2026 07:11:13 +0000</v>
-      </c>
-      <c r="C24" t="str">
-        <v>"alertas.empresas.millenniumbcp.pt" &lt;alertas.empresas.millenniumbcp.pt@cansidro.info&gt;</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Documentos em formato digital</v>
-      </c>
-      <c r="E24" t="str">
-        <v>Estimado(a) Cliente, Enviamos o documento em formato digital (.pdf): Documentos em formato digital do movimento feito na conta 45556587090 para que possa consultar de forma r&amp;aacute;pida e c&amp;oacute;moda. No site, basta fazer login e ir a "Opera&amp;ccedil;&amp;otilde;es Banc&amp;aacute;rias &gt; Outros Servi&amp;ccedil;os &gt; Documentos &gt; Notas de Lan&amp;ccedil;amento" para ter acesso aos documentos emitidos nos &amp;uacute;ltimos 12 meses. Caso pretenda receb&amp;ecirc;-lo noutro email, aceda a "Alertas &gt; Notas de Lan&amp;ccedil;amento" e, na op&amp;ccedil;&amp;atilde;o "Criar Novo", indique o novo endere&amp;ccedil;o. J&amp;Aacute; CONHECE A APP M EMPRESAS ? Instale j&amp;aacute; e fa&amp;ccedil;a a gest&amp;atilde;o da sua Empresa a partir do smartphone. Simples, r&amp;aacute;pida e intuitiva! Com os melhores cumprimentos, millenniumbcp.pt Este e-mail &amp;eacute; apenas informativo, n&amp;atilde;o responda a este endere&amp;ccedil;o. Estes e-mails n&amp;atilde;o permitem o acesso direto ao Site do Millennium bcp, n&amp;atilde;o incluem atalhos (links)* nem s&amp;atilde;o utilizados para solicitar quaisquer elementos identificativos ou c&amp;oacute;digos de acesso. Se n&amp;atilde;o pretende receber e-mails do tema em ep&amp;iacute;grafe, envie um e-mail para a caixa: extratodigital.remover.campanhas@millenniumbcp.pt com o assunto "Remover". Se n&amp;atilde;o pretende receber mais e-mails publicit&amp;aacute;rios do Millennium bcp, envie um e-mail para a caixa: tudo.remover.campanhas@millenniumbcp.pt com o assunto "Remover tudo". Banco Comercial Portugu&amp;ecirc;s, S.A., registado no Banco de Portugal sob o n&amp;ordm;. 33; Sede: Pra&amp;ccedil;a D. Jo&amp;atilde;o I, 28, 4000-295 Porto; Capital Social: 3.000.000.000 euros; N&amp;uacute;mero &amp;uacute;nico de matr&amp;iacute;cula e de identifica&amp;ccedil;&amp;atilde;o fiscal: 501525882 (Conservat&amp;oacute;ria do Registo Comercial do Porto). *Alguns servi&amp;ccedil;os de e-mail assumem, automaticamente, links em certas palavras, sem qualquer responsabilidade por parte do Millennium bcp. 91 850 45 04 &amp;bull; 93 050 45 04 &amp;bull; 96 150 41 26 (chamada para rede m&amp;oacute;vel nacional) +351 21 004 24 24 (chamada para rede fixa nacional) Dispon&amp;iacute;vel todos os dias das 08h &amp;agrave;s 22h, hora de Portugal Continental. O custo das comunica&amp;ccedil;&amp;otilde;es depende do tarif&amp;aacute;rio acordado com o seu operador.</v>
-      </c>
-      <c r="F24" t="str">
-        <v>SPAM</v>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v>0</v>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27018.json</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>27182</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Tue, 11 Aug 2026 15:53:55 +0000</v>
-      </c>
-      <c r="C25" t="str">
-        <v>"karla" &lt;info@retesp.com&gt;</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Solicitação de Cotação e Especificações do Pedido – Agosto de 2026</v>
-      </c>
-      <c r="E25" t="str">
-        <v>Prezada Equipe, Espero que estejam bem. Poderiam, por favor, compartilhar o preço, o prazo de entrega e os requisitos para os seguintes modelos de produto, com base no documento anexo? Agradeceríamos o envio de sua cotação assim que possível. Atenciosamente, _Melhores cumprimentos / Saludos / Best Regards_ _ _ _"Jesus é a nossa Bandeira de Vitória!" "¡Jesús es nuestra Bandera de la Victoria!"_ _ "Jesus is our Banner of Victory!"_ _ ​_ ​</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Pedido de Informação</v>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v>0</v>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27182.json</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>27448</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Thu, 17 Sep 2026 11:07:38 +0100</v>
-      </c>
-      <c r="C26" t="str">
-        <v>geral@sacastro-ferragens.com</v>
-      </c>
-      <c r="D26" t="str">
-        <v>RE: EC1117 - Globalbrico - SA CASTRO - COMERCIO DE FERRAGENS, LDA - Encomenda de Cliente nº 12160.PDF</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Bom dia, Agradecemos o vosso pedido e enviamos em anexo a respetiva nota de encomenda para verificação detalhada de todos os elementos. Mais informamos que os prazos de entrega indicados são uma previsão à data de hoje, baseada nos prazos médios de fornecimento e disponibilidade atual, reservando-nos o direito de os ajustar em função da disponibilidade de stock ou constrangimentos logísticos. Esta e as restantes condições de venda encontram-se detalhadas na nota de encomenda em anexo. Estamos à disposição para qualquer questão adicional. Obrigada pela preferência e confiança. Respeitosos Cumprimentos, De: GLOBALBRICO Encomendas Enviada: 17 de setembro de 2026 10:54 Para: geral@sacastro-ferragens.com Assunto: Re: EC1117 - Globalbrico - SA CASTRO - COMERCIO DE FERRAGENS, LDA Bom dia, Cor inox. Melhores cumprimentos, João Vilela. &gt; escreveu (quinta, 17/09/2026 à(s) 09:37): Bom dia, Espero que se encontre bem. Agradeço que nos confirmem, por favor, qual o acabamento que pretendem. https://www.sacastro-ferragens.com/pt/detalhes/1773 Qualquer dúvida disponha,. Muito obrigada Respeitosos Cumprimentos, De: GLOBALBRICO Encomendas &gt; Enviada: 16 de setembro de 2026 18:28 Para: geral@sacastro-ferragens.com Assunto: EC1117 - Globalbrico - SA CASTRO - COMERCIO DE FERRAGENS, LDA Exmo. Senhor(a), Em anexo a nossa encomenda a fornecedor nº1117 (Fechadura para barra anti-panico - imagem em anexo) Caso não tenham para entrega, solicito que informem. Por favor, colocar na fatura o nosso nº de encomenda. Melhores cumprimentos, Sem vírus. www.avg.com -- Este e-mail foi analisado pelo software antivírus AVG para verificar a presença de vírus. www.avg.com</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Pedido de Encomenda</v>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v>0</v>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27448.json</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>27449</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Thu, 17 Sep 2026 11:18:28 +0100</v>
-      </c>
-      <c r="C27" t="str">
-        <v>"Nivel Padrao" &lt;nivelpadrao@gmail.com&gt;</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Re: Proposta para botas de proteção individual</v>
-      </c>
-      <c r="E27" t="str">
-        <v>Bom dia, Têm alguma bota em loja para experimentar? Cumprimentos, Filipe Costa Em qua., 16 de set. de 2026 às 17:48, GLOBALBRICO Encomendas escreveu: &gt; Boa tarde, &gt; &gt; Agradecemos desde já a consulta efetuada. &gt; &gt; Tal como solicitado, segue em anexo o orçamento pretendido, aguardando uma &gt; vossa resposta. &gt; &gt; Obrigado, &gt; &gt; Melhores cumprimentos, &gt; &gt; &gt; &gt; &gt; Nivel Padrao escreveu (segunda, 14/09/2026 à(s) &gt; 16:21): &gt; &gt;&gt; Boa tarde, &gt;&gt; &gt;&gt; Conforme combinado, venho por este meio solicitar a vossa melhor proposta &gt;&gt; para botas de protecção S3 com seguinte os números: &gt;&gt; &gt;&gt; . 1 par nº 39 &gt;&gt; . 1 par nº40 &gt;&gt; . 5 pares nº41 &gt;&gt; . 2 pares nº42 &gt;&gt; . 2 pares nº43 &gt;&gt; . 1 pares nº44 &gt;&gt; &gt;&gt; Melhores cumprimentos, &gt;&gt; Filipe Costa (929 120 755) &gt;&gt; « Chamada para a rede móvel nacional» &gt;&gt; &gt;</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Pedido de Informação</v>
-      </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v>0</v>
-      </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27449.json</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>27450</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Thu, 17 Sep 2026 12:34:13 +0100</v>
-      </c>
-      <c r="C28" t="str">
-        <v>"GLOBALBRICO Apoio ao Cliente" &lt;apoioaocliente@globalbrico.pt&gt;</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Fwd: Pedido de orçamento formal para materiais, ferramentas e equipamentos – Rodrigo &amp; Soares, Lda.</v>
-      </c>
-      <c r="E28" t="str">
-        <v>---------- Forwarded message --------- De: Rodrigo Soares Date: quinta, 17/09/2026 à(s) 11:44 Subject: Pedido de orçamento formal para materiais, ferramentas e equipamentos – Rodrigo &amp; Soares, Lda. To: Exmos. Senhores, No âmbito da candidatura aos apoios de recuperação de prejuízos causados por incêndios na nossa exploração agrícola, vimos por este meio solicitar a V. Exas. o envio de um orçamento formal para os seguintes artigos disponíveis no vosso catálogo: - *01 Compressor de ar* – Qtd: 1 - *01 Rebarbadora* – Qtd: 1 - *01 Extensão em rolo com enrolador (50m)* – Qtd: 1 - *02 Pás* de agricultura – Qtd: 2 - *02 Extintores F27A 6Kg* – Qtd: 2 - *06 Prateleiras de arrumação metálicas* – Qtd: 6 - *01 Mesa de apoio de trabalho* – Qtd: 1 - *01 Desenrolador de arame* – Qtd: 1 - *Tintas e diluentes* para manutenção – Qtd: 1 conjunto Agradecemos que a proposta comercial discrimine explicitamente: - Os valores unitários e totais de cada artigo; - O valor do IVA aplicável; - Os custos de transporte/portes de entrega (ou indicação para levantamento); - O prazo de entrega estimado e a validade da proposta (requisito obrigatório para o processo de candidatura). Certos da vossa melhor atenção, aguardamos o envio do documento formal. Com os melhores cumprimentos, *Altamiro Soares* Rodrigo &amp; Soares, Lda. NIF: 510923135 Telemóvel: 968 080 690 --</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Pedido de Informação</v>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v>0</v>
-      </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27450.json</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>27453</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Thu, 17 Sep 2026 16:54:30 +0100</v>
-      </c>
-      <c r="C29" t="str">
-        <v>"Pedro - Cardoso Leal" &lt;pedro@cardosoleal.com&gt;</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Encomenda - CARDOSO LEAL</v>
-      </c>
-      <c r="E29" t="str">
-        <v>Boa tarde, Envio em anexo a seguinte encomenda. Alguma dúvida não hesite em nos contactar. Os melhores cumprimentos / Cordialement / Best Regards, Pedro Cardoso Leal Rua Stª. Marinha - nº 53 | 4595-349 Penamaior | Paços de Ferreira | Tel: +351-255 891 587 | www.cardosoleal.com</v>
-      </c>
-      <c r="F29" t="str">
-        <v>Pedido de Encomenda</v>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v>0</v>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27453.json</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>27455</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Thu, 17 Sep 2026 17:47:41 +0000</v>
-      </c>
-      <c r="C30" t="str">
-        <v>"Jorge Carvalho Fibrosom" &lt;jorge.carvalho@fibrosom.com&gt;</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Proposta Fibrosom</v>
-      </c>
-      <c r="E30" t="str">
-        <v>Boa tarde, Conforme solicitado envio proposta em anexo. Enviado de Outlook para Android</v>
-      </c>
-      <c r="F30" t="str">
-        <v>SPAM</v>
-      </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="L30" t="str">
-        <v>0</v>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27455.json</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>27456</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Thu, 17 Sep 2026 21:07:58 +0100</v>
-      </c>
-      <c r="C31" t="str">
-        <v>"Jose Dias" &lt;pladurtec2025@gmail.com&gt;</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Re:</v>
-      </c>
-      <c r="E31" t="str">
-        <v>Exmos Srs Pergunto quais as condições de pagamento. Aguardo vossas noticias Muito obrigado Pacto100Fim Unipessoal Lda NIF.519345347 Telm.937453810 pladurtec2025@gmail.com José Manuel A quarta, 16/09/2026, 18:07, GLOBALBRICO Encomendas escreveu: &gt; Boa tarde &gt; &gt; Carregador e bateria são separados. &gt; &gt; Envio em anexo proposta c/ carregador e baterias, juntamente com o valor &gt; dos pregos. &gt; &gt; Aguardo uma v/ resposta, &gt; &gt; Melhores cumprimentos, &gt; &gt; &gt; &gt; &gt; &gt;&gt; &gt;&gt; &gt;&gt; ---------- Mensagem encaminhada --------- &gt;&gt; From: Jose Dias &gt;&gt; Data: dom., 13/09/2026 às 18:38 &gt;&gt; Assunto: &gt;&gt; Para: &gt;&gt; &gt;&gt; &gt;&gt; Pregadora para betão a bateria ref.TCLNI9005 27/40 mm pergunto se vem &gt;&gt; bateria e carregador incluido no preço. &gt;&gt; Qual o preço de cada cx.pregos &gt;&gt; Aguardo suas noticias para seguir com a compra. &gt;&gt; Cumprimentos &gt;&gt; Pacto100Fim Unipessoal Lda &gt;&gt; Rua dos Diogos,14 &gt;&gt; &gt;&gt; 8950-411 &gt;&gt; &gt;&gt; Altura-Castro Marim &gt;&gt; &gt;&gt; &gt;&gt; NIF.519345347 &gt;&gt; Pladurtec2025@gmail.com &gt;&gt; &gt;&gt; &gt;&gt;</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Pedido de Informação</v>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v>0</v>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27456.json</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>27457</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Fri, 18 Sep 2026 09:00:04 +0100</v>
-      </c>
-      <c r="C32" t="str">
-        <v>jobraga@jobraga.com</v>
-      </c>
-      <c r="D32" t="str">
-        <v>RE: Pedido cotação - Globalbrico - Jobraga</v>
-      </c>
-      <c r="E32" t="str">
-        <v>Bom dia, Segue em anexo orçamento Cumprimentos Daniel Machado Jobraga – Comércio de Ferragens, Lda Rua do Arinho, Pav. 1A, nº17 4705-629 Sequeira - Braga Tel. (+351) 253674821 (chamadas para rede fixa nacional) Site: www.jobraga.com De: GLOBALBRICO Encomendas Enviada: 17 de setembro de 2026 10:56 Para: jobraga@jobraga.com Assunto: Re: Pedido cotação - Globalbrico - Jobraga Bom dia, Podem enviar orçamento do caixote em preto, com a frente em preto. Melhores cumprimentos, João Vilela. &gt; escreveu (quinta, 17/09/2026 à(s) 09:03): Bom dia, Podemos vender as caixas em bruto e depois de vocês lacarem entregam cá e o nosso fornecedor faz a montagem, ou se o caixote for preto e só vão lacar a frente, pode vir só a frente e depois de vocês lacarem entregam cá e o nosso fornecedor faz a montagem. Qual das opções querem? Cumprimentos Daniel Machado Jobraga – Comércio de Ferragens, Lda Rua do Arinho, Pav. 1A, nº17 4705-629 Sequeira - Braga Tel. (+351) 253674821 (chamadas para rede fixa nacional) Site: www.jobraga.com De: GLOBALBRICO Encomendas &gt; Enviada: 16 de setembro de 2026 16:48 Para: jobraga@jobraga.com Assunto: Re: Pedido cotação - Globalbrico - Jobraga Boa tarde. No acabamento que for mais barato, pois o artigo vai ser lacado pelo cliente a cor de outros artigos no mesmo local. Melhores cumprimentos, &gt; escreveu (quarta, 16/09/2026 à(s) 11:52): Bom dia, Qual a cor da frente da caixa de correio? O caixote e o aro são em preto? Cumprimentos Daniel Machado Jobraga – Comércio de Ferragens, Lda Rua do Arinho, Pav. 1A, nº17 4705-629 Sequeira - Braga Tel. (+351) 253674821 (chamadas para rede fixa nacional) Site: www.jobraga.com De: GLOBALBRICO Encomendas &gt; Enviada: 16 de setembro de 2026 11:45 Para: jobraga@jobraga.com Assunto: Pedido cotação - Globalbrico - Jobraga Bom dia Espero encontrá-los bem ! Somos uma empresa de revenda de artigos diversos (máquinas/ bricolagem e construção) em Paços de Ferreira. Solicitamos cotação e condições de venda para o seguinte artigo.: 150 - Caixa de correio J4750 1f Dubral Aguardamos uma v/ resposta, Melhores cumprimentos,</v>
-      </c>
-      <c r="F32" t="str">
-        <v>SPAM</v>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <v>0</v>
-      </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
-      <c r="N32" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27457.json</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>27458</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Fri, 18 Sep 2026 09:06:32 +0000</v>
-      </c>
-      <c r="C33" t="str">
-        <v>"Diana Costa" &lt;Diana.Costa@prugent.com&gt;</v>
-      </c>
-      <c r="D33" t="str">
-        <v>RE: Pedido de Informação | Rodizios</v>
-      </c>
-      <c r="E33" t="str">
-        <v>Olá, Por favor cancelar esta encomenda . Cumprimentos | Best regards | Bien cordialement | Mit freundlichen Grüßen Diana Costa Rua da Gandarela, 185 | 4590-326 Freamunde | Portugal +351912605982 www.prugent.com [cid:image001.png@01DD4755.5FC71DE0] De: Diana Costa Enviada: 17 de setembro de 2026 15:16 Para: GLOBALBRICO Encomendas Cc: João SOARES ; Luisa ALVES ; Miguel CARDOSO Assunto: RE: Pedido de Informação | Rodizios Boa tarde, Eu quero iguais aos 251223 – Rodizio 120/B-160 Mecanarte mas com travão. Nós compramos esta semana os direcionais e agora queremos iguais mas com travão. Cumprimentos | Best regards | Bien cordialement | Mit freundlichen Grüßen Diana Costa Rua da Gandarela, 185 | 4590-326 Freamunde | Portugal +351912605982 www.prugent.com [cid:image001.png@01DD4755.5FC71DE0] De: GLOBALBRICO Encomendas &gt; Enviada: 17 de setembro de 2026 10:32 Para: Diana Costa &gt; Assunto: Re: Pedido de Informação | Rodizios EMAIL EXTERNO : O remetente deste email é externo ao grupo DIAM. Tenha especial cuidado com o seu conteúdo e não abra links ou anexos inesperados ou suspeitos. Bom dia, Conforme falado anteriormente, necessitamos que nos indique qual pretendem. Enviamos novamente as imagens com as medidas mais aproximadas. Melhores cumprimentos, João Vilela. Diana Costa &gt; escreveu (quinta, 17/09/2026 à(s) 08:25): Bom dia, Pode encomendar 4 unidades? Cumprimentos | Best regards | Bien cordialement | Mit freundlichen Grüßen Diana Costa Rua da Gandarela, 185 | 4590-326 Freamunde | Portugal +351912605982 www.prugent.com [cid:image001.png@01DD4755.5FC71DE0] De: GLOBALBRICO Encomendas &gt; Enviada: 16 de setembro de 2026 17:52 Para: Diana Costa &gt; Assunto: Re: Pedido de Informação | Rodizios EMAIL EXTERNO : O remetente deste email é externo ao grupo DIAM. Tenha especial cuidado com o seu conteúdo e não abra links ou anexos inesperados ou suspeitos. Boa tarde Apenas por encomenda. Melhores cumprimentos, [https://ci3.googleusercontent.com/mail-sig/AIorK4zM88fzrydrwcWoMtYpz9-7Yqq8gGzFIkFwwZtN4RhGS0RB0GP0ApLFbxU_9qBApqpU77m031SEfadc] Diana Costa &gt; escreveu (quarta, 16/09/2026 à(s) 15:39): Olá, Têm estas rodas com travão? Cumprimentos | Best regards | Bien cordialement | Mit freundlichen Grüßen Diana Costa Rua da Gandarela, 185 | 4590-326 Freamunde | Portugal +351912605982 www.prugent.com [cid:image001.png@01DD4755.5FC71DE0] De: Diana Costa Enviada: 15 de setembro de 2026 15:51 Para: encomendas@globalbrico.pt Cc: Armazem GERAL &gt;; João SOARES &gt;; Luisa ALVES &gt;; Miguel CARDOSO &gt;; Kévin SEGARD &gt; Assunto: RE: Pedido de Informação | Rodizios Boa tarde, Estas rodas já chegaram? Cumprimentos | Best regards | Bien cordialement | Mit freundlichen Grüßen Diana Costa Rua da Gandarela, 185 | 4590-326 Freamunde | Portugal +351912605982 www.prugent.com [cid:image001.png@01DD4755.5FC71DE0] De: Diana Costa Enviada: 28 de agosto de 2026 08:31 Para: encomendas@globalbrico.pt Cc: Armazem GERAL &gt;; João SOARES &gt;; Luisa ALVES &gt;; Miguel CARDOSO &gt;; Kévin SEGARD &gt; Assunto: Pedido de Informação | Rodizios Bom dia, Preciso de rodízios iguais aos da imagem com as seguinte especificações: * Furação: * QTY: 20 unidades [cid:image002.png@01DD4755.5FC71DE0] Cumprimentos | Best regards | Bien cordialement | Mit freundlichen Grüßen Diana Costa Rua da Gandarela, 185 | 4590-326 Freamunde | Portugal +351912605982 www.prugent.com [cid:image001.png@01DD4755.5FC71DE0]</v>
-      </c>
-      <c r="F33" t="str">
-        <v>SPAM</v>
-      </c>
-      <c r="G33" t="str">
-        <v/>
-      </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
-      <c r="I33" t="str">
-        <v/>
-      </c>
-      <c r="L33" t="str">
-        <v>0</v>
-      </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
-      <c r="N33" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27458.json</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>27459</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Fri, 18 Sep 2026 09:34:31 +0000</v>
-      </c>
-      <c r="C34" t="str">
-        <v>"Márcia Costa" &lt;marcia.costa@cm-pacosdeferreira.pt&gt;</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Pedido de orçamento N.º 488</v>
-      </c>
-      <c r="E34" t="str">
-        <v>Exmo. Senhor(a), Vimos por este meio solicitar envio da V/melhor proposta de orçamento, para o que passamos a especificar: 8 Unidades - Cimento Cola Weber-col Classic Branco-25kg 200 KG - Cimento cola cinzento -&gt;Com entrega incluída nas Oficinas Municipais: Rua Joaquim Martins, nº 78 - 4595-242 Meixomil; -&gt; IMPORTANTE: indicar o prazo de entrega em caso de adjudicação; -&gt;Aguardamos propostas até às 17H00 do dia 21-09-2026. Informações importantes para admissão das propostas: - Apenas serão admitidos orçamentos rececionados dentro da data estipulada e para o seguinte email: gabinetedecompras@cm-pacosdeferreira.pt com a indicação dos prazos de entrega e fichas técnicas dos materiais que propuserem (quando aplicável). Devem ainda indicar sempre o nosso número de pedido de orçamento; - Para obter informações sobre adjudicação do procedimento em causa, entrar em contacto com o gabinete de compras, através do contacto de email gabinetedecompras@cm-pacosdeferreira.pt ou telefone 255 860 781, indicando sempre o n.º do respetivo pedido de orçamento. Solicita-se que apenas o façam cerca de duas semanas após data de término para receção de propostas. Informações importantes em caso de adjudicação: - Para pagamento (ENTRE 30 a 60 DIAS após receção de fatura ou conforme acordado, após boa receção dos bens/serviços) é necessário ceder autorização de consulta online das Certidões de Nao Dívida às Finanças e à Segurança Social, indicando o v/ NISS. O NISS do município é: 20003548855. Em caso de não cederem autorização o envio deverá ser feito para os email: geral@cm-pacosdeferreira.pt ou paula.leao@cm-pacosdeferreira.pt ; - É obrigatória a identificação do n.º requisição na própria fatura sob pena de devolução da mesma; - OBRIGATORIEDADE DE EMISSÃO DE FATURA ELETRÓNICA PREVISTA NO ARTIGO 299º - B DO CÓDIGO DOS CONTRATOS PÚBLICOS, os fornecedores da Administração Pública são obrigados a emitir faturas eletrónicas no âmbito da execução de contratos públicos, conforme o disposto no artigo 299. ºB do Código dos Contratos Público (CCP); Faturação Eletrónica, no âmbito da contratação pública (art.º 299-B) Formatos aceites Métodos de envio Faturas em formato PDF geral@cm-pacosdeferreira.pt paula.leao@cm-pacosdeferreira.pt Faturas em formato impresso (papel) Via Correio postal endereçado ao Município PF Faturação eletrónica Através de solução EDI (XML) - Broker YET * (*) O processo de EDI efetua-se através do envio para, faturacao.eletronica@cm-pacosdeferreira.pt , do ficheiro XML, CIUS-PT acompanhado de um PDF com a imagem da fatura que deverá ser certificada digitalmente. O ficheiro XML terá de ter obrigatoriamente os dados que devem constar da fatura, incluindo o número de compromisso. O Município valida este número e a fatura não será aceite se o mesmo for inválido.Em caso de dúvida, deverá contactar os serviços de contabilidade do Município. O nosso prestador de serviços (Broker) é YET - Your Electronic Transactions. Certos da melhor atenção para o exposto e na expectativa de notícias positivas da V/parte, subscrevemo-nos, Melhores cumprimentos Márcia Veiga Gabinete de Compras Contacto Direto: 255 860 781 [cid:cmpf.png]</v>
-      </c>
-      <c r="F34" t="str">
-        <v>Pedido de Informação</v>
-      </c>
-      <c r="G34" t="str">
-        <v/>
-      </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-      <c r="I34" t="str">
-        <v/>
-      </c>
-      <c r="L34" t="str">
-        <v>0</v>
-      </c>
-      <c r="M34" t="str">
-        <v/>
-      </c>
-      <c r="N34" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27459.json</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>27460</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Fri, 18 Sep 2026 11:07:48 +0100</v>
-      </c>
-      <c r="C35" t="str">
-        <v>miguel.silva@zegnea.com</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Pedido de cotação</v>
-      </c>
-      <c r="E35" t="str">
-        <v>Bom dia, Solicito, por favor, a cotação para o fornecimento de 5 un. de Sika® Separol® Universal, 25 L. A cotação deverá ser efetuada com o NIF 502 753 420 e a entrega na seguinte morada: Rua de Santa Eulália, n.º 387  Tabuadelo 4835-458 Tabuadelo  Guimarães Obrigado. Cumprimentos, Miguel Silva Departamento de Compras Tel.: 918086009 Travessa João de Oliveira Salgado, 32, Costa 4810-015 Guimarães Telf. 253 565 098 (chamada para rede fixa nacional)</v>
-      </c>
-      <c r="F35" t="str">
-        <v>Pedido de Informação</v>
-      </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
-      <c r="I35" t="str">
-        <v/>
-      </c>
-      <c r="L35" t="str">
-        <v>0</v>
-      </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
-      <c r="N35" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27460.json</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>27462</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Fri, 18 Sep 2026 14:39:43 +0000</v>
-      </c>
-      <c r="C36" t="str">
-        <v>"Cristina Pacheco" &lt;cristina.pacheco@ada.pt&gt;</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Encomenda CP260918</v>
-      </c>
-      <c r="E36" t="str">
-        <v>Boa tarde, Encomendo seguinte material, mas preciso que me informem se posso recolher na 2ª feira logo pela manhã: 4 caixas cola e veda branca soudal, igual á última compra. 2 latas tela líquida cinza 4un tubos cola e veda alta temperatura. Com os melhores cumprimentos, Best Regards, CRISTINA PACHECO Purchase Department| Dep. Compras +351 924 489 683 [Descrição: Descrição: cid:image003.png@01D53B36.F5D57EE0]</v>
-      </c>
-      <c r="F36" t="str">
-        <v>Pedido de Encomenda</v>
-      </c>
-      <c r="G36" t="str">
-        <v/>
-      </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
-      <c r="I36" t="str">
-        <v/>
-      </c>
-      <c r="L36" t="str">
-        <v>0</v>
-      </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
-      <c r="N36" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27462.json</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>27463</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Sat, 19 Sep 2026 09:18:43 +0100</v>
-      </c>
-      <c r="C37" t="str">
-        <v>"Globalbrico Geral" &lt;geral@globalbrico.pt&gt;</v>
-      </c>
-      <c r="D37" t="str">
-        <v>FW: Tabela</v>
-      </c>
-      <c r="E37" t="str">
-        <v>Obrigado Com os melhores cumprimentos, De: Comercial Enviada: 18 de setembro de 2026 18:10 Para: Comercial Assunto: Tabela Boa tarde, Segue em anexo a nossa tabela de preços atualizada. Com os melhores cumprimentos/With our Best Regards, Frebrico - Comércio de Bricolage, Lda. Armazém: Rua Delfim Ferreira, Lote 113 Zona Industrial da Maia 1 - Sector VII 4470-436 Maia (Portugal) Sede: Urbanização Industrial do Soeiro, Lote 21 4745-457 S. Mamede do Coronado (Portugal) Tel. (00351) 229 812 438 Fax: (00351) 229 812 440 WEB: www.frebrico.pt E-mail: info@frebrico.pt</v>
-      </c>
-      <c r="F37" t="str">
-        <v>SPAM</v>
-      </c>
-      <c r="G37" t="str">
-        <v/>
-      </c>
-      <c r="H37" t="str">
-        <v/>
-      </c>
-      <c r="I37" t="str">
-        <v/>
-      </c>
-      <c r="L37" t="str">
-        <v>0</v>
-      </c>
-      <c r="M37" t="str">
-        <v/>
-      </c>
-      <c r="N37" t="str">
-        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27463.json</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>27464</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Sat, 19 Sep 2026 20:27:54 +0800</v>
-      </c>
-      <c r="C38" t="str">
-        <v>"MAY" &lt;may@directfactorysp.com&gt;</v>
-      </c>
-      <c r="D38" t="str">
-        <v>***SPAM***  Advanced Magnetic Components for Your Designs</v>
-      </c>
-      <c r="E38" t="str">
-        <v>Hi Encomendas, I hope this message finds you well. Further to our previous discussion on power supplies, I wanted to introduce the extensive line of Magnetic Components. These components are critical for ensuring efficiency and compliance in modern electronics. The High Current Power Inductors are a prime example of the innovation available: Engineered with flat wire and powder molding for high performance. Achieve high saturation currents up to 150Amps with low core losses. Magnetically shielded designs to minimize acoustic noise and interference, with AEC-Q200 qualified options. These components are designed to provide a competitive advantage in both performance and cost. Would a sample of our High Current Power Inductors be helpful for your team's evaluation? May Sales Manager K-well Tech If you don't want to receive our emails, you can easily unsubscribe here.</v>
-      </c>
-      <c r="F38" t="str">
-        <v>SPAM</v>
-      </c>
-      <c r="G38" t="str">
-        <v/>
-      </c>
-      <c r="H38" t="str">
-        <v/>
-      </c>
-      <c r="I38" t="str">
-        <v/>
-      </c>
-      <c r="L38" t="str">
-        <v>0</v>
-      </c>
-      <c r="M38" t="str">
-        <v/>
-      </c>
-      <c r="N38" t="str">
         <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27464.json</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/emails_classificacao.xlsx
+++ b/data/emails_classificacao.xlsx
@@ -396,8 +396,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:N23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1219,6 +1219,12 @@
       <c r="I19" t="str">
         <v/>
       </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
       <c r="L19" t="str">
         <v>0</v>
       </c>
@@ -1257,6 +1263,12 @@
       <c r="I20" t="str">
         <v/>
       </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
       <c r="L20" t="str">
         <v>0</v>
       </c>
@@ -1295,6 +1307,12 @@
       <c r="I21" t="str">
         <v/>
       </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
       <c r="L21" t="str">
         <v>0</v>
       </c>
@@ -1333,6 +1351,12 @@
       <c r="I22" t="str">
         <v/>
       </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
       <c r="L22" t="str">
         <v>0</v>
       </c>
@@ -1371,6 +1395,12 @@
       <c r="I23" t="str">
         <v/>
       </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
       <c r="L23" t="str">
         <v>0</v>
       </c>
@@ -1381,9 +1411,85 @@
         <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27464.json</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>27466</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Mon, 21 Sep 2026 08:29:14 +0000</v>
+      </c>
+      <c r="C24" t="str">
+        <v>"Orçamentos" &lt;orcamentos@ribeiroemoreira.com&gt;</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Encomenda</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Exmos. Senhores Segue em anexo encomenda de material. Com os melhores cumprimentos / Best regards / Salutations António Freitas [220011_09__PAPEL_CARTA_1A_page-0001]Ribeiro &amp; Moreira, Lda Avenida das Cerdeiras, nº 127, 4590-653 - Raimonda - Paços de Ferreira - Portugal Tel: 00351 255 881 987 Telem: 00351 918 483 289 NIF: 506 050 327 Ao seu lado com as melhores soluções em arquitectura, caixilharia, alumínio, ferro e construções metálicas... Consulte-nos em www.ribeiroemoreira.com ou por contabilidade@ribeiroemoreira.com ou orcamentos@ribeiroemoreira.com [cid:image003.jpg@01DD49AB.A96C5F70] Antes de imprimir este e-mail pense bem se tem mesmo que o fazer... Proteja o Ambiente, olhe à sua volta, há cada vez menos árvores... AVISO DE CONFIDENCIALIDADE Esta mensagem de correio electrónico e qualquer dos seus ficheiros anexos, caso existam, são confidenciais e destinados apenas à(s) pessoa(s) ou entidade(s) acima referida(s), podendo conter informação confidencial, privilegiada, a qual não deverá ser divulgada, copiada, gravada ou distribuída nos termos da lei vigente. Se não é o destinatário da mensagem, ou se ela lhe foi enviada por engano, agradecemos que não faça uso ou divulgação da mesma. A distribuição ou utilização da informação nela contida é interdita. Se recebeu esta mensagem por engano, por favor avise-nos de imediato, por correio electrónico, para o endereço acima e apague este e-mail do seu sistema. Obrigado.</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>0</v>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27466.json</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>27468</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Mon, 21 Sep 2026 10:15:14 +0100</v>
+      </c>
+      <c r="C25" t="str">
+        <v>"ANIMOVEL - Ana Sousa" &lt;anasousa@animovel.pt&gt;</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Encomenda Fornecedor nº EC2602351</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Esta mensagem foi enviada automaticamente. Para mais esclarecimentos sobre esta mensagem será necessário contactar o remetente. AVISO LEGAL Esta mensagem é confidencial e dirigida apenas ao destinatário. Se a recebeu por erro solicitamos que o comunique ao remetente e a elimine assim como qualquer documento anexo. Não há renúncia à confidencialidade nem a nenhum privilégio devido a erro de transmissão. DISCLAIMER This message is confidential and intended exclusively for the addressee. If you received this message by mistake please inform the sender and delete the message and attachments. No confidentiality nor any privilege regarding the information is waived or lost by any mistransmission. melhores cumprimentos | best regards Esta mensagem, incluindo os ficheiros em anexo, podem conter informações confidenciais, priveligiadas e/ ou legalmente protegidas e é destinada exclusivamente ao(s) destinatário(s) desta mensagem. O seu uso, divulgação, uso ou cópia sem a devida autorização é estritamente proibido. Se não é o destinatário desta mensagem, por favor avise imediatamente o remetente e elimine todas as cópias deste email. This message and its attached files may contain confidential information, priviliged or legally protected and its intended exclusively to the reciever of this message. The unauthorized use, copying, disclosure or sending is strictly forbidden. If you are not the indented recipient of this message please delete it. Ce message incluant des fichiers en p.j peut contenir des informations confidentielles, privilégées et est destine exlcusivemente au(x) destinataire(s) de ce message. Lutilisation non autorisée, divulgation, copie ou envoie est strictement interdite. Si vous nêtes pas le destinataire de ce message, veuillez svp informer immédiatement l expéditeur, éliminez toutes les copies de cet émail.</v>
+      </c>
+      <c r="F25" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>0</v>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27468.json</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/emails_classificacao.xlsx
+++ b/data/emails_classificacao.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N42"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1439,6 +1439,12 @@
       <c r="I24" t="str">
         <v/>
       </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
       <c r="L24" t="str">
         <v>0</v>
       </c>
@@ -1477,6 +1483,12 @@
       <c r="I25" t="str">
         <v/>
       </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
       <c r="L25" t="str">
         <v>0</v>
       </c>
@@ -1487,9 +1499,745 @@
         <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27468.json</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>27474</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Tue, 22 Sep 2026 14:05:00 +0000</v>
+      </c>
+      <c r="C26" t="str">
+        <v>"Igor Salier" &lt;igor.salier@famo.pt&gt;</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Orçamento painel ondulado de rede</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Boa tarde.. Solicito orçamento para 1 painel de rede semelhante às fotos em anexo. 10x10x2mm com 1.50m x 1.20m Obrigado Enviado do meu Galaxy</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Pedido de Informação</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="I26" t="str">
+        <v>0.5237</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>0</v>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27474.json</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>27475</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Tue, 22 Sep 2026 14:14:56 +0000</v>
+      </c>
+      <c r="C27" t="str">
+        <v>"Ribeiro &amp; Moreira | Dep2" &lt;deptecnico2@ribeiroemoreira.com&gt;</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Pedido de Info/Preço -Dobradiças Móveis</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Exmos. Senhores Boa tarde Sr. Pedro, Pode por favor enviar o v/ melhor orçamento para 6 unidades da seguinte dobradiça com as seguintes características: - Copo 35mm - Espaço entre furos: 48mm - Calço de ajuste normal Envio foto de anexo para referência. [cid:image001.png@01DD4AA5.1F86A540] Com os melhores cumprimentos / Best regards / Salutations André Paiva [220011_09__PAPEL_CARTA_1A_page-0001]Ribeiro &amp; Moreira, Lda Avenida das Cerdeiras, nº 127, 4590-653 - Raimonda - Paços de Ferreira - Portugal Tel: 00351 255 881 987 NIF: 506 050 327 Ao seu lado com as melhores soluções em arquitectura, caixilharia, alumínio, ferro e construções metálicas... Consulte-nos em www.ribeiroemoreira.com ou por contabilidade@ribeiroemoreira.com ou orcamentos@ribeiroemoreira.com [cid:image004.jpg@01DD4AA5.1F86A540] Antes de imprimir este e-mail pense bem se tem mesmo que o fazer... Proteja o Ambiente, olhe à sua volta, há cada vez menos árvores... AVISO DE CONFIDENCIALIDADE Esta mensagem de correio electrónico e qualquer dos seus ficheiros anexos, caso existam, são confidenciais e destinados apenas à(s) pessoa(s) ou entidade(s) acima referida(s), podendo conter informação confidencial, privilegiada, a qual não deverá ser divulgada, copiada, gravada ou distribuída nos termos da lei vigente. Se não é o destinatário da mensagem, ou se ela lhe foi enviada por engano, agradecemos que não faça uso ou divulgação da mesma. A distribuição ou utilização da informação nela contida é interdita. Se recebeu esta mensagem por engano, por favor avise-nos de imediato, por correio electrónico, para o endereço acima e apague este e-mail do seu sistema. Obrigado.</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Pedido de Informação</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="I27" t="str">
+        <v>0.9862</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>0</v>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27475.json</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>27477</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Tue, 22 Sep 2026 17:30:49 +0100</v>
+      </c>
+      <c r="C28" t="str">
+        <v>miguel.silva@zegnea.com</v>
+      </c>
+      <c r="D28" t="str">
+        <v>FW: Pedido de cotação</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Miguel Silva Departamento de Compras Tel.: 918086009 Travessa João de Oliveira Salgado, 32, Costa 4810-015 Guimarães Telf. 253 565 098 (chamada para rede fixa nacional) De: miguel.silva@zegnea.com Enviada: 18 de setembro de 2026 11:08 Para: 'encomendas@globalbrico.pt' Assunto: Pedido de cotação Bom dia, Solicito, por favor, a cotação para o fornecimento de 5 un. de Sika® Separol® Universal, 25 L. A cotação deverá ser efetuada com o NIF 502 753 420 e a entrega na seguinte morada: Rua de Santa Eulália, n.º 387  Tabuadelo 4835-458 Tabuadelo  Guimarães Obrigado. Cumprimentos, Miguel Silva Departamento de Compras Tel.: 918086009 Travessa João de Oliveira Salgado, 32, Costa 4810-015 Guimarães Telf. 253 565 098 (chamada para rede fixa nacional)</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Pedido de Informação</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>Pedido de Informação</v>
+      </c>
+      <c r="I28" t="str">
+        <v>0.998</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>0</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27477.json</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>27478</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Tue, 22 Sep 2026 18:00:16 +0100</v>
+      </c>
+      <c r="C29" t="str">
+        <v>"GLOBALBRICO Marketing" &lt;marketing@globalbrico.pt&gt;</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v>--</v>
+      </c>
+      <c r="F29" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="I29" t="str">
+        <v>0.8097</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v>0</v>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27478.json</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>27485</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Wed, 23 Sep 2026 10:25:55 +0000</v>
+      </c>
+      <c r="C30" t="str">
+        <v>"Worten PT" &lt;noreply@info.worten.pt&gt;</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Worten Marketplace | Há Novas Categorias no Marketplace</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Há Novas Categorias no Marketplace! HÁ NOVAS CATEGORIAS NO MARKETPLACE! O que é? A revisão geral de atributos tem como objetivo fazer a revisão do catálogo de todas as categorias e ajustar os atributos de cada categoria de acordo com a necessidade de cada unidade de negócio ou de acordo com a lei (atributos legais obrigatórios). O que foi feito nesta revisão?Foram criadas novas categorias. Consultar a listagem aqui .Revisão de obrigatoriedades de atributos em grande parte das categorias do nosso Marketplace. Consultar listagem de atributos por categoria aqui . Quando vão ser implementadas as alterações? Entrada em vigor a 29 de setembro de 2026. 🚨 Importante A revisão de atributos foi realizada em praticamente todas as categorias de marketplace Worten (consultar listagem acima). Esta revisão implica a revisão do mapeamento de atributos (por exemplo, que antes eram recomendados e especiais e agora são obrigatórios). É importante rever as configurações dos mapeamentos para garantir que o catálogo de produtos está em conformidade com esta alteração. 🚨 Novos Atributos Legais: Novo Aviso e Rótulo Harmonizados para Garantias de Bens, com entrada em vigor a 27 de setembro de 2026. Consultar todas as informações e mais detalhes aqui . Quando será a próxima revisão de atributos? Expectavelmente, a próxima revisão de atributos será feita dentro de 6 meses. Se tiver alguma dúvida ou necessitar de esclarecimentos adicionais, contacte a nossa equipa através de um ticket no Seller Center . Our mailing address is: , , To unsubscribe from future emails click this unsubscribe link https://unsub.insightlyunsubscribe.com/Unsubscribe/Unsubscribe?key=OTkyNDExLTM0NjA2OTMxMg%3D%3D.</v>
+      </c>
+      <c r="F30" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="I30" t="str">
+        <v>0.5726</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v>0</v>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27485.json</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>27489</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Wed, 23 Sep 2026 13:33:41 +0000</v>
+      </c>
+      <c r="C31" t="str">
+        <v>"Márcia Costa" &lt;marcia.costa@cm-pacosdeferreira.pt&gt;</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Pedido de orçamento N.º 190 + 263</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Exmo. Senhor(a), Vimos por este meio solicitar envio da V/melhor proposta de orçamento, para o que passamos a especificar: Pedido Nº263 1 Uni. - Rebitadora a Bateria METABO ou equivalente NP 18LTX BL 5,0, com 2 baterias 18V-4Ah LIHD + carregador ASC 55 1 Uni. - Martelo combinado METABO ou equivalente KH 18 LTX 24, com 2 baterias 18V-4Ah lipower + carregador ASC 55, força de impacto: 2.1J 1 Uni. - Bucha para berbequim de aperto rápido 1 Uni. - Martelo combinado METABO ou equivalente KH 18 LTX BL 24 Q (Opção com troca de bucha rápida), com 2 baterias 18V-4Ah LIHD + carregador ASC 55, força de impacto: 2.2J + 1 bucha rápida 1 Uni. - Rebarbadora METABO ou equivalente W 18 7-125, com 2 baterias 18V-4Ah lipower + carregador ASC 55 1 Uni.- Chave de impacto 1" ROTAKE ou equivalente - ref. T6-0 - características: Quadra 1", tensão nominal 20, velocidade sem carga (RPM) 1900/1500/1100, impactos por minuto (IPM) 2400/1900/1400.12 Binário máximo de aperto (Nm) 2200, binário máx. desaperto (Nm) 2500, peso Kg 3,60, medidas: CxLxA (mm) 225x92x235 1 Uni.- Chave de impacto longa 1" ROTAKE ou equivalente- ref. T9-80D - características: Quadra 1", 2 baterias 8.0Ah, carregador 4A 4x4, quadra 1", tensão nominal 40, tipo de motor Brushless, velocidade sem carga (RPM) 1100/700, impactos por minuto (IPM)1600/1300/100015 binário máximo aperto (Nm) 3200, binário máximo desaperto (Nm) 4000, peso Kg 16.50, medidas: CxLxA (mm) 720x409x152 1 Uni. - Soprador ROTAKE ou equivalente- ref.8513-0, características: Tensão nominal (V) 20, Tipo de motor Brush, velocidade do ar (m/s) _70, velocidade nominal (RPM) 18000, peso líquido (Kg) 1,08, dimensões (CxLxA) (mm)550x140x310 Pedido Nº 190 1Uni. - Ferro de soldar estanho 8mm 80w 1Uni. - Chaves macho hexagonal com punho e extremidade esférica 96TBP - BETA, ou equivalente ref. 000960687 1Uni.- Chave de caixa 15 mm, Sextavado - Hazet ou equivalente 1Uni. - Chave macho hexagonal com punho - BETA ou equivalente - ref.000960942 1Uni. - Chave macho hexagonal com punho - BETA ou equivalente - ref.000960692 1Uni.- Bandeja termoformada macia com conjunto de alicates - BETA ou equivalente - ref. M132 1Uni.- Chave de fenda 8x150mm 2Uni.- Chave tipo Phillips ou equivalente 2x100 1Uni. - Conjunto de roquete 3/8" 1000V de 14 peças, ref. TTV- 3814 1Uni. - Mala de ferramenta eletricista: WIHA XXL ou equivalente 4 VDE com 80 peças 10Uni.- X-acto 18mm FATMAX Stanley ou equivalente FMHT10592-0 com sistema de segmentação integrado 100Uni.- Lámina X-acto 18mm 15Mt. - Mangueira de ar comprimido tipo mola com engates rápidos M/F 2Uni.- Pistola d'ar ABAC, ref. G-502 - curto longo 10cm -pressão máxima 8 bares, ou similar 1Uni. -Chave boca/luneta articulada com sistema de roquete Beta ou equivalente - ref. 001420213 ---- 1 Uni. - Máquina de pintura ares 4200 + mangueira + pistola B2000 + Cabeçal + bico 1 Uni. - Máquina motopico BOSCH ou equivalente GSH 11 VC -&gt;Com entrega incluída nas Oficinas Municipais: Rua Joaquim Martins, nº 78 - 4595-242 Meixomil; Nota muito importante: Apenas serão consideradas as propostas que remeterem ficha técnica / fotografia dos artigos propostos. -&gt; IMPORTANTE: indicar o prazo de entrega em caso de adjudicação; -&gt;Aguardamos propostas até às 17H00 do dia 25-09-2026. Informações importantes para admissão das propostas: - Apenas serão admitidos orçamentos rececionados dentro da data estipulada e para o seguinte email: gabinetedecompras@cm-pacosdeferreira.pt com a indicação dos prazos de entrega e fichas técnicas dos materiais que propuserem (quando aplicável). Devem ainda indicar sempre o nosso número de pedido de orçamento; - Para obter informações sobre adjudicação do procedimento em causa, entrar em contacto com o gabinete de compras, através do contacto de email gabinetedecompras@cm-pacosdeferreira.pt ou telefone 255 860 781, indicando sempre o n.º do respetivo pedido de orçamento. Solicita-se que apenas o façam cerca de duas semanas após data de término para receção de propostas. Informações importantes em caso de adjudicação: - Para pagamento (ENTRE 30 a 60 DIAS após receção de fatura ou conforme acordado, após boa receção dos bens/serviços) é necessário ceder autorização de consulta online das Certidões de Nao Dívida às Finanças e à Segurança Social, indicando o v/ NISS. O NISS do município é: 20003548855. Em caso de não cederem autorização o envio deverá ser feito para os email: geral@cm-pacosdeferreira.pt ou paula.leao@cm-pacosdeferreira.pt ; - É obrigatória a identificação do n.º requisição na própria fatura sob pena de devolução da mesma; - OBRIGATORIEDADE DE EMISSÃO DE FATURA ELETRÓNICA PREVISTA NO ARTIGO 299º - B DO CÓDIGO DOS CONTRATOS PÚBLICOS, os fornecedores da Administração Pública são obrigados a emitir faturas eletrónicas no âmbito da execução de contratos públicos, conforme o disposto no artigo 299. ºB do Código dos Contratos Público (CCP); Faturação Eletrónica, no âmbito da contratação pública (art.º 299-B) Formatos aceites Métodos de envio Faturas em formato PDF geral@cm-pacosdeferreira.pt paula.leao@cm-pacosdeferreira.pt Faturas em formato impresso (papel) Via Correio postal endereçado ao Município PF Faturação eletrónica Através de solução EDI (XML) - Broker YET * (*) O processo de EDI efetua-se através do envio para, faturacao.eletronica@cm-pacosdeferreira.pt , do ficheiro XML, CIUS-PT acompanhado de um PDF com a imagem da fatura que deverá ser certificada digitalmente. O ficheiro XML terá de ter obrigatoriamente os dados que devem constar da fatura, incluindo o número de compromisso. O Município valida este número e a fatura não será aceite se o mesmo for inválido.Em caso de dúvida, deverá contactar os serviços de contabilidade do Município. O nosso prestador de serviços (Broker) é YET - Your Electronic Transactions. Certos da melhor atenção para o exposto e na expectativa de notícias positivas da V/parte, subscrevemo-nos, Melhores cumprimentos Márcia Veiga Gabinete de Compras Contacto Direto: 255 860 781 [cid:cmpf.png]</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Pedido de Informação</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>Pedido de Informação</v>
+      </c>
+      <c r="I31" t="str">
+        <v>0.9916</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v>0</v>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27489.json</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>27492</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Wed, 23 Sep 2026 17:02:22 +0000</v>
+      </c>
+      <c r="C32" t="str">
+        <v>"Orçamentos" &lt;orcamentos@ribeiroemoreira.com&gt;</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Encomenda</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Exmos. Senhores Com os melhores cumprimentos / Best regards / Salutations António Freitas [220011_09__PAPEL_CARTA_1A_page-0001]Ribeiro &amp; Moreira, Lda Avenida das Cerdeiras, nº 127, 4590-653 - Raimonda - Paços de Ferreira - Portugal Tel: 00351 255 881 987 Telem: 00351 918 483 289 NIF: 506 050 327 Ao seu lado com as melhores soluções em arquitectura, caixilharia, alumínio, ferro e construções metálicas... Consulte-nos em www.ribeiroemoreira.com ou por contabilidade@ribeiroemoreira.com ou orcamentos@ribeiroemoreira.com [cid:image003.jpg@01DD4B85.AD405170] Antes de imprimir este e-mail pense bem se tem mesmo que o fazer... Proteja o Ambiente, olhe à sua volta, há cada vez menos árvores... AVISO DE CONFIDENCIALIDADE Esta mensagem de correio electrónico e qualquer dos seus ficheiros anexos, caso existam, são confidenciais e destinados apenas à(s) pessoa(s) ou entidade(s) acima referida(s), podendo conter informação confidencial, privilegiada, a qual não deverá ser divulgada, copiada, gravada ou distribuída nos termos da lei vigente. Se não é o destinatário da mensagem, ou se ela lhe foi enviada por engano, agradecemos que não faça uso ou divulgação da mesma. A distribuição ou utilização da informação nela contida é interdita. Se recebeu esta mensagem por engano, por favor avise-nos de imediato, por correio electrónico, para o endereço acima e apague este e-mail do seu sistema. Obrigado.</v>
+      </c>
+      <c r="F32" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="I32" t="str">
+        <v>0.994</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v>0</v>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27492.json</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>27496</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Thu, 24 Sep 2026 11:33:19 +0000</v>
+      </c>
+      <c r="C33" t="str">
+        <v>"Jose Carvalho" &lt;jose.carvalho1@inter.ikea.com&gt;</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Pedido orçamento de compressor 12bar - RFQ_BOF_MANT_000928</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Bom dia! Venho por este meio solicitar o seguimento orçamento, seguindo sempre as seguintes indicações quando é solicitado : 1. Sendo mencionado no pedido, colocar na respetiva orçamentação o nº, RFQ ????(Nosso código de pedido de orçamentação), como indicado em baixo ; 2. Numero de ordem interna a que chamamos TPM ; 3. Prazo de respostas entre 1 e 2 dias úteis , salvo casos urgentes que serão mencionados ; 4. Cada pedido deverá ser independente do outro (orçamentos individuais). 5. Prazo de entrega 6. Incluir sempre o assunto do pedido RFQ Qt. Descrição Data pedido WO RFQ_BOF_MANT_000928 1 Pedido de compressor capacidade 12bar amovivel para se deslocar aos equipamentos (Empilhadores GT) 1 - Objetivo alimentar macaco troca pneus( 8 a 12 bar) 2 - Verificar pressão pneus , 10bar 24-09-2026 N/A Nota: Cumprimentos / Best Regards / Vänliga hälsningar José Carvalho Maintenance BOF - L&amp;P and Foil IKEA Industry Paços de Ferreira Mobile: +351 935 111 991 (ext: 5770) The information in this e-mail is confidential and may be legally privileged. It is intended solely for the addressee. Access to this e-mail by anyone else is unauthorized. If you are not the intended recipient, any disclosure, copying, distribution, or any action taken or omitted to be taken in reliance on it, is prohibited and may be unlawful. Bom dia! Precismsos Internal</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Pedido de Informação</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="I33" t="str">
+        <v>0.8057</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v>0</v>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27496.json</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>27498</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Thu, 24 Sep 2026 12:42:55 +0000</v>
+      </c>
+      <c r="C34" t="str">
+        <v>"Diana Costa" &lt;Diana.Costa@prugent.com&gt;</v>
+      </c>
+      <c r="D34" t="str">
+        <v>PRUGENT DIAM PORTUGAL - ENCF 41396</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Estimados Senhores/as, Envio em anexo a requisição do material/ serviço pretendido. Pedimos por favor confirmação do valor da encomenda bem como do prazo de entrega da mesma. Atenção, por favor enviar a respetiva fatura para os emails: * office.pdp@prugentdiam.com * diana.costa@prugent.com Aguardo confirmação. Cumprimentos | Best regards | Bien cordialement | Mit freundlichen Grüßen Diana Costa Rua da Gandarela, 185 | 4590-326 Freamunde | Portugal +351912605982 www.prugent.com [cid:image001.png@01DD4C2A.99180AD0]</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="I34" t="str">
+        <v>0.9616</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v>0</v>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27498.json</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>27499</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Thu, 24 Sep 2026 13:22:08 +0000</v>
+      </c>
+      <c r="C35" t="str">
+        <v>"Banco BPI" &lt;info@diagofinances.com&gt;</v>
+      </c>
+      <c r="D35" t="str">
+        <v>***SPAM***  Comprovativo de pagamento</v>
+      </c>
+      <c r="E35" t="str">
+        <v>BANCO BPI Hola encomendas O pagamento de 6.300 euros está a caminho. PDF Cópia do comprovativo de pagamento (EUR 6.300).pdf Consultar documento Obrigada. Com os melhores cumprimentos, Sandra Vilas Boas Gestor de Negócios Balcão de Barcelos TM: 931 847 485 R. Pe. Alfredo Rocha Martins Edf. Apolo, 55, Lj. 4 - 4750-255 Barcelos</v>
+      </c>
+      <c r="F35" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="I35" t="str">
+        <v>1</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v>0</v>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27499.json</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>27500</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Thu, 24 Sep 2026 15:32:02 +0000</v>
+      </c>
+      <c r="C36" t="str">
+        <v>"João Bessa" &lt;joaobessa@amfurnituregroup.com&gt;</v>
+      </c>
+      <c r="D36" t="str">
+        <v>EF 3844 AMF</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Boa tarde, Segue em anexo uma nova encomenda. Aguardo confirmação da data de entrega, por favor Obrigado, [cid:image002.png@01DD4C42.3778A970]Melhores cumprimentos | Best Regards João Bessa Compras | Purchase Department mobile. + 351 938 563 702 phone. + 351 255 860 390 [rodape_email-07] [rodape_email-09] [rodape_email-08] | Help Us Improve [rodape_email-04] [cid:image007.png@01DCAC8C.E0672FD0] [cid:7359a24d-4594-437c-a3a2-516694ba2e03] [cid:eb0472cc-bd62-475c-9cd8-207189405db9]</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="I36" t="str">
+        <v>0.8851</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v>0</v>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27500.json</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>27503</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Thu, 24 Sep 2026 17:30:26 +0000</v>
+      </c>
+      <c r="C37" t="str">
+        <v>"Carlos Manuel Aniceto Falcão" &lt;cfalcao@rubi.com&gt;</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Proposta nivelamento Cyclone</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Boa tarde. Ref.35951 - caixa de campânulas com 1200 unidades avulso Ref.35939 - caixa de distanciadores com 2400 unidades avulso Ref.35945 - caixa de distanciadores com 2400 unidades avulso Preço válido para uma compra mínima de 10 caixas, podendo misturar as 3 referências. Cumprimentos. CARLOS MANUEL ANICETO FALCÃO Rubi Portugal Sales Representative (North) ​ ​ Confidentiality Notice &amp; Data Protection Compliance</v>
+      </c>
+      <c r="F37" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>Pedido de Informação</v>
+      </c>
+      <c r="I37" t="str">
+        <v>0.8718</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v>0</v>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27503.json</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>27504</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Fri, 25 Sep 2026 09:32:38 +0100</v>
+      </c>
+      <c r="C38" t="str">
+        <v>"Compras Serralharia da Recta" &lt;compras.srecta@gmail.com&gt;</v>
+      </c>
+      <c r="D38" t="str">
+        <v>encomenda</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Exmo. (s) Sr. (s). Bom dia 1 LATA DE 5 LITROS GRIS 7042 CINZENTO, VOU JÁ LEVANTAR OBRIGADA. Vimos por este meio *encomendar* o material em anexo. Agradecemos desde já o vosso melhor prazo de entrega, se for caso de sermos nós a levantar é o favor de nos avisar. Muito Obrigado Sem outro assunto de momento, subscrevemo-nos com os melhores cumprimentos. De V. Exª( s). Atentamente, Luís Silva *Dept. Compras* compras.srecta@gmail.com [image: Logo] *E: *geral@serralhariadarecta.com *T: *+351 255 962 062 «chamada para a rede fixa nacional» *M: *Rua Recta de Gomil, nº77/83, 4595-144 Frazão www.serralhariadarecta.com/ [image: facebook icon] [image: instagram icon] O conteúdo desta mensagem de correio eletrónico é confidencial e destina-se apenas ao destinatário especificado na mensagem. É estritamente proibido partilhar qualquer parte desta mensagem com terceiros, sem o consentimento escrito do remetente. Se recebeu esta mensagem por engano, responda a esta mensagem e proceda à sua eliminação, para que possamos garantir que tal erro não ocorra no futuro.</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>Pedido de Informação</v>
+      </c>
+      <c r="I38" t="str">
+        <v>0.6317</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v>0</v>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27504.json</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>27505</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Fri, 25 Sep 2026 08:51:29 +0000</v>
+      </c>
+      <c r="C39" t="str">
+        <v>"Produção" &lt;producao@ribeiroemoreira.com&gt;</v>
+      </c>
+      <c r="D39" t="str">
+        <v>EF 749/2026</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Bom dia, Segue em anexo encomenda. Têm disponivel para levantamento? Com os melhores cumprimentos / Best regards / Salutations Bruna Alves Tel: 00351 255 881 987 Fax: 00351 255 881 814[220011_09__PAPEL_CARTA_1A_page-0001] Ribeiro &amp; Moreira, Lda Avenida das Cerdeiras, nº 127, 4590-653 - Raimonda - Paços de Ferreira - Portugal NIF: 506 050 327 Ao seu lado com as melhores soluções em arquitectura, caixilharia, alumínio, ferro e construções metálicas... Consulte-nos em www.ribeiroemoreira.com ou por contabilidade@ribeiroemoreira.com ou orcamentos@ribeiroemoreira.com [cid:image003.jpg@01DD4CD3.6E681BF0] Antes de imprimir este e-mail pense bem se tem mesmo que o fazer... Proteja o Ambiente, olhe à sua volta, há cada vez menos árvores... AVISO DE CONFIDENCIALIDADE Esta mensagem de correio electrónico e qualquer dos seus ficheiros anexos, caso existam, são confidenciais e destinados apenas à(s) pessoa(s) ou entidade(s) acima referida(s), podendo conter informação confidencial, privilegiada, a qual não deverá ser divulgada, copiada, gravada ou distribuída nos termos da lei vigente. Se não é o destinatário da mensagem, ou se ela lhe foi enviada por engano, agradecemos que não faça uso ou divulgação da mesma. A distribuição ou utilização da informação nela contida é interdita. Se recebeu esta mensagem por engano, por favor avise-nos de imediato, por correio electrónico, para o endereço acima e apague este e-mail do seu sistema. Obrigado.</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="I39" t="str">
+        <v>0.9915</v>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v>0</v>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27505.json</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>27507</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Fri, 25 Sep 2026 14:23:42 +0100</v>
+      </c>
+      <c r="C40" t="str">
+        <v>"Unatudo" &lt;unatudo@gmail.com&gt;</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Tabelas em anexo SIKA</v>
+      </c>
+      <c r="E40" t="str">
+        <v>*Bom dia!* *Caro(a) e Estimado(a) Senhor(a)* Desejamos que se encontre bem *Proposta:* Tabela da Sika Construção: Ao PVP SIKA : Tem 50% de desconto, para encomenda por caixa do produto Tem 50 % + 10% de desconto para palete do mesmo produto Segue em anexo Descontos intermédios para alguns produtos em quantidade inferior a uma Palete Tabela da Sika Industria : Tem 30% de desconto, para encomenda por caixa de produto * Temos sempre uma boa solução para si* * A UNATUDO é um distribuidor SIKA , SOUDAL , MAPEI e BONA.* * Consulte-nos * [image: Sika - O Sikagard®-790 All-in-One Protect é a proteção invisível para fachadas, pavimentos e coberturas! O produto protege contra a água, óleos e manchas sem alterar a aparência das superfícies. Para além] [image: Soudal Portugal | Sintra][image: Mapei Portugal | Produtos para a Construção][image: SOPREMA Portugal | LinkedIn] [image: Batendo Recordes] *S&amp;O* *Siga-nos em : **https://w **ww.facebook.com/Unatudo * * Caso haja dúvidas não hesitem em contactar-nos.* *R*ecebe esta informação porque solicitou/é cliente/fornecedor. Cordialmente e ao dispor *Jacinto Rocha * * UNATUDO - SOLUÇÕES TÉCNICAS de COLAGEM LDA* * NIF 504 067 958* Rua Valmarinhas 31/37 4445 225 Alfena ( Valongo) * unatudo@gmail.com www.unatudo.pt https://www.facebook.com/Unatudo * * Fone (+351) 229670171 (custo de chamada local para a rede fixa nacional)* * Telemóvel/ WhatsApp (+351) 911141491 - 935945914 - 964094598* * (custo de chamada local para a rede móvel nacional )*</v>
+      </c>
+      <c r="F40" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>Pedido de Encomenda</v>
+      </c>
+      <c r="I40" t="str">
+        <v>0.6207</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v>0</v>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27507.json</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>27510</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Mon, 28 Sep 2026 06:00:02 +0000</v>
+      </c>
+      <c r="C41" t="str">
+        <v>compras@inovocorte.pt</v>
+      </c>
+      <c r="D41" t="str">
+        <v>ENCOMENDAS: Notificação de atrasos de entrega</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Exmos. Srs., Vimos por este meio informar que as seguintes encomendas já ultrapassaram o prazo previsto para entrega: N.Encomenda N.Artigo Descrição Qt.Falta Un. Dt.Entrega Atraso (dias) ENF-SY022607/0034 MC00-00002806 PONTAS / ADAPTADOR P/APARAFUSADORA SHOCKWAVE HEX.4X25MM MILWAUKEE (EMB. 2 UN) 4 UN 2026-09-25 3 ENF-SY022607/0034 MC00-00003441 CHAVE SEXTAVADA METRICASTANDARD C/CABO EM T 2.5X125MM(2 LAMINAS) 3 UN 2026-09-25 3 ENF-SY022607/0034 MC00-00002804 PONTAS / ADAPTADOR P/APARAFUSADORA SHOCKWAVE HEX.5X25MM MILWAUKEE (EMB. 2 UN) 4 UN 2026-09-25 3 Agradecemos confirmação urgente do novo prazo de entrega deste material. Nota: Caso já tenham efetuado a entrega ignorem esta mensagem e por favor indiquem o n.º do vosso documento de acompanhamento. Aguardamos resposta a este e-mail com a maior celeridade. Atentamente, Compras Inovocorte - compras@inovocorte.pt</v>
+      </c>
+      <c r="F41" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="I41" t="str">
+        <v>0.995</v>
+      </c>
+      <c r="L41" t="str">
+        <v>0</v>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27510.json</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>27513</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Mon, 28 Sep 2026 07:31:09 +0000</v>
+      </c>
+      <c r="C42" t="str">
+        <v>"João Ribeiro" &lt;joao.ribeiro@mail.clarmaj.com&gt;</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Esta empresa pagou anúncios e só ligaram particulares</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Cometeram 3 erros básicos Olá Encomendas@globalbrico.pt, Recentemente recebemos este caso em mãos. Uma empresa de metalomecânica, que atua no fabrico de peças por subcontratação para fábricas, pagou anúncios no Google e até tiveram resultados numa fase inicial. Eram pedidos de orçamento, contudo, do outro lado estavam particulares a pedir orçamento para portões, portas e gradeamento. Vinham totalmente desqualificadas. Muitos donos de empresa param aqui e concluem que o Google não serve para o setor deles. Nos casos que analisamos, o dinheiro perde-se quase sempre em duas ou três escolhas feitas no inicio do lançamento da campanha. Saiba aqui o que foi mal feito neste projeto, onde perderam dinheiro, o que deveriam ter feito corretamente. Google Ads para Industria [https://email.mail.clarmaj.com/c/eJxsk02PsjoAhX8N7MZA-SgsWICCzqCAjg6jG1NKwQptkU_1198475ubm9zZnrSnp-fkwWeaOzs3fO9Wp9Mhgcfvj2E8Insv544GM03OBUOUOwzReoZr1DJ0nWHB_upnMXHSdhfanPtHQ5xaYNRT8UfPZeKo0FYMSzGhIpOXx5mRrkMleT3blKnmET86xOXi4I0sKdLV31M_ZhixBtGS_0d7XTNRZoMCZXZBkKlZWLGswtYNUyZ8pK3gjPDeaVqRD_gVRb44BsyAlqs6zHRbtWGGNVMBSoENrNmmakCZOkABpmIDS4GaqtgzaCBd1VCRm6pqEduUdOV_DdTOpe-bTtJcCQQSCFDXkb6b4ZzPClqTDhVk1jUIEwkElhovv3I3mJbP-Fbfh-MjFxIIGMkpkkDw-pIGCghJoRvAMg2kAF03zNm1IaVc4_OfBijvSctR7RxA0OXLr-pblUDwnqiEbaGP3YAi8ch3xbLPnupKa9k9tkm5iJNwsIAtAU9E--m2d8tyeYgv6Y6fFmmy2LwX23R-sd1jNSWetkrK2_0ogUA9VV0VrOa82j_T0wN_8nINfbzCEvBSb3jWH4ntp1O4FHtjrkL_UAeFqLyMSiCYqBuHCd0N8Xe51rZ-goSlLr-86RGNeoDUsqx31iOD-9UQKnt2xVE0pgZz3eELhtFpUVMCw3AKMGja3SO377cFrSTgzal_eRRLb82Ddy8z5mo7lBsJBP5tSb41NG_W1h3vixH6mrUtdaFY5ecuCq_1HbMoQjt6gsyPT8_rYnv5jNNoaJ5UPJ_QHD7gJkwk4HnRfj2fkt5zD5vbRgLewjRHLQ4n_9qrmDU8NEx_V2C6qOjDzm-e3fLV9i7X4gel34aWGekvIndQQ2XR0pJyJxvq6u1nVLlpxUhz0jo1QTkWnBPci1ZuHcKxYITnqJN0paxFhuqspVjMml7uxNBi4vw4vNFufJtEW5FW7l8Enn8N0TtYsPOvqPcO6c__0jY64J8AAAD__0ZoYHE] [https://email.mail.clarmaj.com/c/eJxslE9zsjoYxT8N7NqBoPxZsBABtVhAq9W6cUISMEIShADip79j23vnzrzv9jdPTs48OSfoTLG7nUWrdnk67VPr6_jW9V_Q2anYNazMULFgkHKXQVq9ogo2DF5fkWC__CwGTpr2QuuzHGviVgJBScUPxypxdcvRprZmWppKnhpnRtoWFuR5bV0cDI8E8T4p_L3XszQ_LH-nvsUQZDWkBf8fex4zYeaAHGZOTqBp2Eiz7dyZTE2V8J42gjPCpVs3AnfoaUW9uKbtEJTZGOUOBMTKMqhjZBCiGQhAQ9NU6gINmJoDbM0ydM15taZwohswx6au28QxlYn2xwYq9yJl3SrGTAGhAsKK8vKVtUXLcfMcUED4bfxFNhCVlBcKCE2c5SjHAGSmYoRIcAmRXGHF8NccHHWW3O9LmaMxOV61Va8As5Ps3IquQUQx_G-5X8gIph37F6oVOv9siXJJGg4rdw_CFi8-y6OugHCV6oRtrADNQgrFiLf5QmYPfWk07J44pPCTNOps4CjAE_FuuO1mRbHYJ5fDlp_8Q-q_r_LNYX5xZl_lkHrGMi1u9y8FhPqpbMtwOefl7nE4jeiDF2srQEukAO_gdY_qLXWCwxAtxG46161gX4W5KL2MKiAc6CyJUrrtkmOxNjZBCoWtLz69YYz7SQj1oqi29phZu2UXaTt2RXHcH6ZsNus-rSg--RUlVhQNIQJ1sx2xc7_5tFSAN6fBZcwX3pqHKy-bzvWmK94VEAa3BTkacF6v7Tva5b0VGPammAjNLj62cXSt7ojFMdzSk8WC5PS4-pvLR3KIu_pBxeNhmd2b9R6lCvC8eLeeD6n0Zvv327sCPN80eyOJhuAqdcRqHk3NYJsj6pd0dPDNcxq-3NzVSnzXzdaTxSeehcPikdyqe_c1YqEyIi8Cu7CmqmhoQbmbdVX58vO6dSN6iknjVgRiJDgnSIpGbVzCkWCEY9gqE62oRAarrKFIvNZS_YmN-5NB2vYvg2hK0qjy2dLzX01IFwl2_ut3IF0iz_81snfBPwEAAP__naRw7g marketing] 3 Erros Básicos no Google Ads [https://email.mail.clarmaj.com/c/eJxslEFzsjoYhX8N7NqBoEAWLERBLRbQarVunJAEjJAEIYD66-_Y9t65M9-3febNyZk35wSfGPE2k2jZLo7HXep8Hd66_gvBrU48y8ksnUiOmPA4YtUrrlDD0eUVS_7LT3IQtGnPrD6pe029SmKkmPzhRKee6UBj7Bq2Y-j0qXHitG1RQZ_X1sXe8mkQ75JitvN7nub7xe_UtxhGvEasEP9jz2M2yiDIUQZzimzLxYbr5nA0tnUqetZIwalQXt1I0uGnFf3sjahlYjiChpkR03BHmUUNYI9dl7jYoRDqzAMGsA0IXMOxTAO-OmM0Mi2UE9s0XQptbWT8sYHKOytVt5o10UCogbBionzlbdEK0jwHNBB-G39RDcIlE4UGQoIs5ACARxBqVoilUAirJdGs2UqAg8mT222hcnxPDhdj2WvA7hQ_tbJrMNWs2bfcL-SUsI7_C_UKn362xISijUCVtwNhS-af5cHUQLhMTcrXToAnIUPyTjb5XGUPc2E1_JZAWsySNOpcADXgy3g7XLeTopjvkvN-I46zfTp7X-br_fQMJ1_lkPrWIi2uty8NhOaxbMtwMRXl9rE_3vGHKFZOgBdYA_7e7x7VWwqD_RDN5XY8NZ1gV4W5LP2MaSAc2CSJUrbpkkOxstZBiqRrzj_94R73oxCZRVFt3HvmbBddZGz5Bcdxvx_zyaT7dKL4OKsYdaJoCDGom82dwNt1xkoN-FMWnO_53F-JcOln46nZdMW7BsLgOqcHC03rlXvD27x3AstdFyNpuMXHJo4u1Q3zOEYbdnR4kBwfl9n6_JHs465-MPl4OHb35rxHqQZ8P96upkOq_Mnu_fquAX9m272VRENwUSbmtYjGdrDJMZuV7A7J1YeNWKxveiW_6-aayfyTTMJh_kiu1a37uhOpc6rOknioZrpsWMGEl3VV-fLzunUje0Zo41UUESyFoFjJRm88KrDkVBDUaiOjqGSGqqxhWL7WSv-JjfeTQdb2L4NsStro6tnS019NKA9Lfvrrd6A8qk7_NbL3wD8BAAD__3orbvo marketing] Cumprimentos, Equipa Clarmaj geral@clarmaj.com [joao.ribeiro@clarmaj.com] +351 [tel: 351000000000]918797551 clarmaj.com [https://email.mail.clarmaj.com/c/eJxslE9zsjoYxT8N7NqBoPxZsBABtVhAq9W6cUIIGCEJhgDip79j23vnzrzv9jdPTs48OSfoTHJ3O4tW7fJ02qfW1_Gt67-gs1Nz17AyQ805hYS5FJL6FdVQUHh9RZz-8jMfGBbthTRnOTbYrTmCkvAfnqvY1S1Hm9qaaWkqfmqcKW5bWOLntU15MDwcxPuk9PdeT9PisPyd-hZDkDaQlOx_7HnMhJkDCpg5BYamYSPNtgtnMjVVzHoiOKOYSbcRPO_Q04p6cTPHsDDWnOnEBlqBdGA7FizAFMLJpHCgrhIXaMDUHGBrlqFrzqs1hRPdgEVu6rqNHVOZaH9soHYvUjatYswUECogrAmrXmlbtiwXzwEFhN_GX6SAqCKsVEBo2pah5YWpT6FihIgzCZFc5Yrhrxk46jS535eyQGNyvGqrXgFmJ-m55Z1AWDH8b7lfSHFOOvovVGt0_tkSYRILBmt3D8I2X3xWR10B4SrVMd1YAZqFBPIx3xYLmT30pSHoPXFw6Sdp1NnAUYDH491w283KcrFPLoctO_mH1H9fFZvD_OLMvqoh9YxlWt7uXwoI9VPVVuFyzqrd43Aa0Qcr11aAlkgB3sHrHvVb6gSHIVrw3XSuW8G-DgteeRlRQDiQWRKlZNslx3JtbIIUcltffHrDGPeTEOplWW_tMbN2yy7SdvSK4rg_TOls1n1aUXzya4KtKBpCBBqxHXPnfvNJpQBvToLLWCy8NQtXXjad66Ir3xUQBrcFPhpw3qztO9oVvRUY9qaccM0uP7ZxdK3viMYx3JKTRYPk9Lj6m8tHcoi75kH442GZ3Zv1HqUK8Lx4t54PqfRm-_fbuwI83zR7I4mG4Cp1RBsWTc1gWyDiV2R08pvnCLbc3NWaf9fN1pPFZz4Lh8UjudX37mvMuUqxvPDchQ1RuSAlYW7W1dXLz-s2gvckx8KtMcwRZwwjyYUqXMwQp5jlsFUmWlnzDNaZIIi_NlL9iY37k0HS9i8DFxUWqny29PxXE9JFnJ7_-h1IF8vzf43sXfBPAAAA__8eLW8m marketing] · LinkedIn [https://email.mail.clarmaj.com/c/eJxslE9zsjoYxT8N7NqBRPmzYCEKarGAVqt144QkYIQkCAHUT3_HtvfOnXnf7W-enJx5ck7wiRFvM4mW7eJ43KX21-Gt67-Qu9WJB-0M6kRyxITHEatecYUaji6vWPJffpKDoE17ZvVJ3WvqVRIjxeQPJzr1TNs1xo5h2YZOnxonTtsWFfR5bV3soU-DeJcUs53f8zTfL36nvsUw4jVihfgfex6zUOaCHGVuTpEFHWw4Tu6OxpZORc8aKTgVyqsbSTr8tKKfPWJBKxvZlgMJxDSzXUAhtrHhIjKm1sjVmQcMYBkucAwbmob7ao_RyIQoJ5ZpOtS1tJHxxwYq76xU3WpwooFQA2HFRPnK26IVpHkOaCD8Nv6iGoRLJgoNhARZAGKSOxnUYIilUAirJdHgbCXAweTJ7bZQOb4nh4ux7DVgdYqfWtk1mGpw9i33CzklrOP_Qr3Cp58tMaFoI1Dl7UDYkvlneTA1EC5Tk_K1HeBJyJC8k00-V9nDXMCG3xKXFrMkjToHuBrwZbwdrttJUcx3yXm_EcfZPp29L_P1fnp2J1_lkPpwkRbX25cGQvNYtmW4mIpy-9gf7_hDFCs7wAusAX_vd4_qLXWD_RDN5XY8Ne1gV4W5LP2MaSAc2CSJUrbpkkOxgusgRdIx55_-cI_7UYjMoqg2zj2zt4suMrb8guO434_5ZNJ92lF8nFWM2lE0hBjUzeZO3Nt1xkoN-FMWnO_53F-JcOln46nZdMW7BsLgOqcHiKb1yrnhbd7bAXTWxUgaTvGxiaNLdcM8jtGGHW0eJMfHZbY-fyT7uKsfTD4ettW92e9RqgHfj7er6ZAqf7J7v75rwJ9ZVg-TaAguysS8FtHYCjY5ZrOS3V1y9d1GLNY3vZLfdXPMZP5JJuEwfyTX6tZ93YnUOVVnSTxUM102rGDCy7qqfPl53bqRPSO08SqKCJZCUKxkozceFVhyKghqtZFRVDJDVdYwLF9rpf_ExvvJIGv7l0E2JW109Wzp6a8mlIclP_31O1AeVaf_Gtl74J8AAAD__2Ydb-0 marketing] Marketing com Mentalidade Industrial If you no longer wish to receive these emails you may unsubscribe [https://email.mail.clarmaj.com/c/eJxsVE23qjgQ_DWwux4I3wsWIqCIgvpUlI0nhIgRQpBP8dfP0ftm5p2Zu-1UV9XpThe6kNTcTX2vWcTxYaOdT8uuP0Njz6empCUSnzIKSWlSSIoJKmBN4X2CGP1dv7ChxHVzI9WlHStsFgzBlrDvespjU9QMQdEFVRN4_Oa4UNw0MMNv2SqLJAs7wSHM7IPV0801WvxGfcgQpBUkWflH7d2mwsQAV5gYVwxVSUeCrl8NWVF5XPakZiXFZWtWNUs79LbC30xFSVRNxqKeqooqYkUQ9GsCZS1VBFkykpQnJhCAKhhAFzRJFIyJpkBZlOA1VUVRx4bKycL_JlCYt7atGk6acsDlgNvguicINxPaZE2Z1m8QB9yP-YYDbtKRIsU1B9yubLqkQTVJ8FdP8MABVxfD-TGdusP8FT6KZ3ceU8YBd1WCk0jD53PRXtEYnu6C13PSNycn2bhEjOIyhQ0HFFnICpbAIqkJYpOq5YD677A5yf5p3BxQW0LxpWkhrTjJ_ntdqq7L8vuR5bh8C43LWzJHJCRL7_DyxIB4jVfuFDTzVC-vTsfZ0pjgcdnAaEtC4snrg7E40p21K9MFzo1nsriJ0anIk9FrPBpU8afx2a2L7JkcDBk7NyGmgbIXb4-1UwCPDCSOhLdgkdCgT6JjF8_d13aeNgl4m1mOMAr6VWkJbywCQY_mhzd-QPRI49Onr0AfveKWzjx1vUfK2j7Ia_sMwoUwGaW00E6WHiRDMl3OyqqPBXXZ1eepSA_72r_s_WI9S-9D4_EFunz_QlK2uC5hYR6A26TzY34SOeB6GxHTreagqUsgG9Pddd4mL3Eh1fQZGjizw43f6cDggMWC_fDYT7Nsfghv0a6M7Whjr73rNprdjOk5HzaWtNhkj-eZA64Y503uLmZlvn9F8Yh-ldlKc9ACccCKrO5VLDeGEw3-nO2Vmag5h8K9stxKCAfcgUxDf0N2XXjKVtLW2UCmi_OjNYxBL7tQzLJip4-Jtl90vrCndxQEfaTQ6bQ7an4Q2wXBmu8PLgJVvRtT4_mwSc4Ba0ac23idW6vS9axEmYl1l6054DqPOT5JcFat9CfaX3vNkfRtJjNBz37tAv9ePBENArgjsUadMH7d7e3tVxgFXfUi7PXS1G6prf0NBywr2K9mw6a1pof1Y80By1bVXgr9wbm3IqJV6Suqs7siYudkNNKHZdTlYvvkC_aJs59uiae4vbHUhBXhWU0yUppJV-Rfn6XyVc16kuLaLDBMEStLjFpW87X5x4H997z4hnU1wuaH4Ys0_dfA6hzXfPtOwcuPJloTMXr5MW5bE7eXfxKvN8FfAQAA__91D-ZQ]</v>
+      </c>
+      <c r="F42" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>SPAM</v>
+      </c>
+      <c r="I42" t="str">
+        <v>0.9732</v>
+      </c>
+      <c r="L42" t="str">
+        <v>0</v>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v>/home/alex/Desktop/classification_globalbrico/data/globalbrico_emails/27513.json</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N42"/>
   </ignoredErrors>
 </worksheet>
 </file>